--- a/naver-place-crawler/results_derma/송도_피부과.xlsx
+++ b/naver-place-crawler/results_derma/송도_피부과.xlsx
@@ -564,34 +564,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>맑고고운시그니처의원 인천연수동춘점</t>
+          <t>파크뷰의원 송도</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pinkclean0713@naver.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>rat3427@naver.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>nsdparkview83@gmail.com</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1497-1523</t>
+          <t>032-710-1404</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 먼우금로 88 5층 501, 502호</t>
+          <t>인천광역시 연수구 하모니로 158 B동 6층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.incheonsignature.com/</t>
+          <t>https://www.youtube.com/@뷰티의정석-w9e</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>539</v>
       </c>
       <c r="R2" t="n">
-        <v>277</v>
+        <v>756</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1037963149</t>
+          <t>1378532253</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037963149</t>
+          <t>https://m.place.naver.com/place/1378532253</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,34 +662,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>플랜유의원</t>
+          <t>리더스피부과의원 송도</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>obnoxious38997@naver.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>bongpaul@naver.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>master@beautyleader.co.kr</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1393-9913</t>
+          <t>032-715-8190</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-15 송도더퍼스트시티 2층 210호</t>
+          <t>인천광역시 연수구 센트럴로 194 더샵센트럴파크2차 A동 2층 리더스피부과의원 송도</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.planuclinic.co.kr/</t>
+          <t>https://leaders-sd.com/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1223</v>
+        <v>464</v>
       </c>
       <c r="Q3" t="n">
-        <v>3342</v>
+        <v>4812</v>
       </c>
       <c r="R3" t="n">
-        <v>4565</v>
+        <v>5276</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1091669936</t>
+          <t>1581468228</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1091669936</t>
+          <t>https://m.place.naver.com/place/1581468228</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -752,34 +760,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>실버라이닝의원</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>silver_lining_songdo@naver.com</t>
-        </is>
-      </c>
+          <t>드림피부과</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1465-8112</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-15 제2층 제201호~제205호</t>
+          <t>인천광역시 연수구 청능대로 210 스퀘어원</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://silverlining.clinic</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -800,22 +800,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1081885317</t>
+          <t>4170845550</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1081885317</t>
+          <t>https://m.place.naver.com/place/4170845550</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>나다움의원 송도</t>
+          <t>변피부과의원</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nadaumclinic@naver.com</t>
+          <t>orangerealtykorea@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>032-832-1117</t>
+          <t>032-818-4333</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 A동 210-211호</t>
+          <t>인천광역시 연수구 원인재로 286 대림아파트 상가 301호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://www.나다움.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -894,22 +894,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>356</v>
+        <v>257</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>378</v>
+        <v>262</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1498510198</t>
+          <t>13240993</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1498510198</t>
+          <t>https://m.place.naver.com/place/13240993</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,44 +940,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피즈벨머의원</t>
+          <t>실버라이닝의원</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>psbellment@naver.com</t>
+          <t>silver_lining_songdo@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1319-6862</t>
+          <t>0507-1465-8112</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-14 301호~304호</t>
+          <t>인천광역시 연수구 해돋이로 160-15 제2층 제201호~제205호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/psbellment</t>
+          <t>https://silverlining.clinic</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>194</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="R6" t="n">
-        <v>7</v>
+        <v>427</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2036564067</t>
+          <t>1081885317</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036564067</t>
+          <t>https://m.place.naver.com/place/1081885317</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>오블리브의원 송도</t>
+          <t>맑고고운시그니처의원 인천연수동춘점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>oblivclinic@naver.com</t>
+          <t>pinkclean0713@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1350-9120</t>
+          <t>0507-1497-1523</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로132번길 34 2층, 3층</t>
+          <t>인천광역시 연수구 먼우금로 88 5층 501, 502호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.obliv.kr/</t>
+          <t>https://www.incheonsignature.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1373</v>
+        <v>277</v>
       </c>
       <c r="Q7" t="n">
-        <v>3502</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>4875</v>
+        <v>282</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1120924408</t>
+          <t>1037963149</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1120924408</t>
+          <t>https://m.place.naver.com/place/1037963149</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1128,44 +1128,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>닥터에버스의원 송도</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>dreverssd03@naver.com</t>
-        </is>
-      </c>
+          <t>미소지움피부과의원</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1360-7570</t>
+          <t>032-832-7775</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 165-17 월드메르디앙 2층</t>
+          <t>인천광역시 연수구 컨벤시아대로 69 송도밀레니엄 509호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://evers17.co.kr/</t>
+          <t>http://www.misoskin.com</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,22 +1172,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>589</v>
+        <v>738</v>
       </c>
       <c r="Q8" t="n">
-        <v>767</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>1356</v>
+        <v>748</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1614509215</t>
+          <t>20393004</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1614509215</t>
+          <t>https://m.place.naver.com/place/20393004</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1222,34 +1218,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>알라딘의원</t>
+          <t>맑고고운의원 옥련송도역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>drjang77@naver.com</t>
+          <t>value_trend_guide@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1467-7894</t>
+          <t>032-832-4051</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 A동 4층</t>
+          <t>인천광역시 연수구 독배로40번길 11 효명프라자 4층 405호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/drjang77</t>
+          <t>https://www.pureskinsongdo.co.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>157</v>
+        <v>948</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="R9" t="n">
-        <v>171</v>
+        <v>998</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1368003991</t>
+          <t>1513557735</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1368003991</t>
+          <t>https://m.place.naver.com/place/1513557735</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1316,44 +1312,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>새로핌피부과의원 인천송도</t>
+          <t>유픽의원 송도</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jzvgcz40jz@naver.com</t>
+          <t>rkdgkwns43210@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>032-833-2777</t>
+          <t>032-256-6010</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 153 2층 207호~211호</t>
+          <t>인천광역시 연수구 해돋이로151번길 4 인피니티타워 6층 601, 602호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://serophim.com/</t>
+          <t>https://www.instagram.com/upic_clinic_Songdo/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1364,7 +1360,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>134</v>
+        <v>510</v>
       </c>
       <c r="Q10" t="n">
-        <v>1607</v>
+        <v>5015</v>
       </c>
       <c r="R10" t="n">
-        <v>1741</v>
+        <v>5525</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2049567933</t>
+          <t>1794584448</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2049567933</t>
+          <t>https://m.place.naver.com/place/1794584448</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에피움의원</t>
+          <t>피어봄의원 송도</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>epium@naver.com</t>
+          <t>pieobom_sd@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>032-818-9979</t>
+          <t>032-818-8275</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로16번길 33-3 C동 2층 207호</t>
+          <t>인천광역시 연수구 센트럴로 160 센트럴파크 푸르지오상가 A동 2층 201~207호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://epium.kr</t>
+          <t>https://songdo.pieobom.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1463,17 +1459,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>312</v>
+        <v>531</v>
       </c>
       <c r="Q11" t="n">
-        <v>1828</v>
+        <v>614</v>
       </c>
       <c r="R11" t="n">
-        <v>2140</v>
+        <v>1145</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2033501340</t>
+          <t>37056636</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033501340</t>
+          <t>https://m.place.naver.com/place/37056636</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1504,34 +1500,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>신피부과의원</t>
+          <t>클렌피부과의원 송도점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>newskin7582@naver.com</t>
+          <t>easy_16878@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1405-7583</t>
+          <t>032-715-4100</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 121 센타프라자 7층 704호</t>
+          <t>인천광역시 연수구 컨벤시아대로230번길 54 송도닥터플러스몰 A동 5층 514-516호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/newskin7582</t>
+          <t>http://pf.kakao.com/_FWtKC</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1541,7 +1537,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1552,7 +1548,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1561,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="R12" t="n">
-        <v>380</v>
+        <v>484</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>19873520</t>
+          <t>1983873176</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19873520</t>
+          <t>https://m.place.naver.com/place/1983873176</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1598,29 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>휴먼피부과의원 송도</t>
+          <t>송도오라클피부과의원</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>humansdm@naver.com</t>
+          <t>songdo_dermatology@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>032-858-3335</t>
+          <t>032-833-2111</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 263 송도IBS타워 업무동 5층</t>
+          <t>인천광역시 연수구 하모니로178번길 6 7층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://www.sdhuman.com/</t>
+          <t>http://songdo-oracle.com/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1630,7 +1626,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1655,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1802</v>
+        <v>819</v>
       </c>
       <c r="Q13" t="n">
-        <v>1464</v>
+        <v>1804</v>
       </c>
       <c r="R13" t="n">
-        <v>3266</v>
+        <v>2623</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>36650530</t>
+          <t>1994869691</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36650530</t>
+          <t>https://m.place.naver.com/place/1994869691</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1692,39 +1688,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>아리엘의원 송도</t>
+          <t>피즈벨머의원</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>clinicariel@naver.com</t>
+          <t>psbellment@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1413-3303</t>
+          <t>0507-1319-6862</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로130번길 14 플러스메디타워 4층 1, 2, 3, 4, 5호</t>
+          <t>인천광역시 연수구 해돋이로 160-14 301호~304호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://arielclinickorea.com/</t>
+          <t>https://blog.naver.com/psbellment</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1740,22 +1736,22 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>5925</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>6243</v>
+        <v>14</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,17 +1760,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1024929142</t>
+          <t>2036564067</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024929142</t>
+          <t>https://m.place.naver.com/place/2036564067</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1786,29 +1782,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>예쁨의정석의원</t>
+          <t>아리엘의원 송도</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jungsukbeauty@naver.com</t>
+          <t>clinicariel@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1371-5609</t>
+          <t>0507-1413-3303</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 20 상가동 2층 216, 217, 218, 221호</t>
+          <t>인천광역시 연수구 컨벤시아대로130번길 14 플러스메디타워 4층 1, 2, 3, 4, 5호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://beautyjungsuk.co.kr</t>
+          <t>https://arielclinickorea.com/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1834,7 +1830,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1843,13 +1839,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>5870</v>
       </c>
       <c r="R15" t="n">
-        <v>100</v>
+        <v>6190</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,17 +1854,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1141240944</t>
+          <t>1024929142</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141240944</t>
+          <t>https://m.place.naver.com/place/1024929142</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1880,44 +1876,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>김지현피부과의원</t>
+          <t>리겐의원 송도</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ohhappysmc@naver.com</t>
+          <t>songdo_st@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>032-817-8083</t>
+          <t>0507-1470-1351</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 청능대로 103 4층</t>
+          <t>인천광역시 연수구 해돋이로152번길 9 8층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.regainclinic.co.kr</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1928,22 +1924,22 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1040</v>
+        <v>419</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="R16" t="n">
-        <v>1050</v>
+        <v>554</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,17 +1948,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>13240981</t>
+          <t>1724640605</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240981</t>
+          <t>https://m.place.naver.com/place/1724640605</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1974,44 +1970,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>닥터포유미앤모의원</t>
+          <t>닥터에버스의원 송도</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>gabewoon@naver.com</t>
+          <t>dreverssd03@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1367-8057</t>
+          <t>0507-1360-7570</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 청능대로 93 이리옴프라자 4층</t>
+          <t>인천광역시 연수구 신송로 165-17 월드메르디앙 2층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/drforu_miandmo/</t>
+          <t>https://evers17.co.kr/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2022,7 +2018,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2031,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>706</v>
+        <v>597</v>
       </c>
       <c r="Q17" t="n">
-        <v>196</v>
+        <v>767</v>
       </c>
       <c r="R17" t="n">
-        <v>902</v>
+        <v>1364</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,17 +2042,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>13574310</t>
+          <t>1614509215</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13574310</t>
+          <t>https://m.place.naver.com/place/1614509215</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2068,44 +2064,44 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>김운호피부과의원</t>
+          <t>리트의원 송도</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cultfind@naver.com</t>
+          <t>ritclinic_director@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>032-813-9212</t>
+          <t>032-833-0107</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 앵고개로 250 연수메디칼빌딩 3층</t>
+          <t>인천광역시 연수구 테크노파크로111번길 15 401, 402호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://ritclinic.co.kr</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2116,22 +2112,22 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1145</v>
+        <v>201</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>2711</v>
       </c>
       <c r="R18" t="n">
-        <v>1149</v>
+        <v>2912</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2140,17 +2136,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13240921</t>
+          <t>1410828317</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240921</t>
+          <t>https://m.place.naver.com/place/1410828317</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2162,39 +2158,43 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>미소지움피부과의원</t>
+          <t>오네스타의원 송도</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>aaprettygirl@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>songdobest1@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>COPYRIGHT2017@HONESTARC.COM</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>032-832-7775</t>
+          <t>032-724-8200</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 69 송도밀레니엄 509호</t>
+          <t>인천광역시 연수구 송도국제대로 157 오네스타몰 4층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://www.misoskin.com</t>
+          <t>http://www.honestarc.com</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2210,22 +2210,22 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>738</v>
+        <v>1634</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="R19" t="n">
-        <v>748</v>
+        <v>1796</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>20393004</t>
+          <t>1824325340</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20393004</t>
+          <t>https://m.place.naver.com/place/1824325340</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>톡스앤필의원 송도</t>
+          <t>필랩의원</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2267,28 +2267,28 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1426-1755</t>
+          <t>0507-873-0537</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층 톡스앤필 송도점</t>
+          <t>인천광역시 연수구 하모니로178번길 22 GTX센트럴빌딩 C동 6층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.toxnfill4.com/</t>
+          <t>https://fill-lab.co.kr</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2309,17 +2309,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>650</v>
+        <v>1040</v>
       </c>
       <c r="Q20" t="n">
-        <v>5570</v>
+        <v>4285</v>
       </c>
       <c r="R20" t="n">
-        <v>6220</v>
+        <v>5325</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2328,17 +2328,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>20618221</t>
+          <t>1358069959</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20618221</t>
+          <t>https://m.place.naver.com/place/1358069959</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2350,29 +2350,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>리겐의원 송도</t>
+          <t>에피움의원</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>songdo_st@naver.com</t>
+          <t>epium@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1470-1351</t>
+          <t>032-818-9979</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로152번길 9 8층</t>
+          <t>인천광역시 연수구 송도과학로16번길 33-3 C동 2층 207호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://www.regainclinic.co.kr</t>
+          <t>https://epium.kr</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2403,17 +2403,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>418</v>
+        <v>349</v>
       </c>
       <c r="Q21" t="n">
-        <v>134</v>
+        <v>1898</v>
       </c>
       <c r="R21" t="n">
-        <v>552</v>
+        <v>2247</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2422,17 +2422,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1724640605</t>
+          <t>2033501340</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1724640605</t>
+          <t>https://m.place.naver.com/place/2033501340</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2444,29 +2444,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>연세마이미의원</t>
+          <t>드림의원</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kti1202@naver.com</t>
+          <t>asdream365@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>032-215-1100</t>
+          <t>032-456-4330</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 166</t>
+          <t>인천광역시 연수구 청능대로 210 3층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://mymii.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>121</v>
+        <v>266</v>
       </c>
       <c r="Q22" t="n">
-        <v>513</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>634</v>
+        <v>268</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2516,17 +2516,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>35507465</t>
+          <t>36476882</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35507465</t>
+          <t>https://m.place.naver.com/place/36476882</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2538,29 +2538,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>밴스의원 송도</t>
+          <t>송도연세피부과의원</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mimimomokk@naver.com</t>
+          <t>yonsei-skindoctor@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>032-710-3037</t>
+          <t>0507-1402-0043</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 11층 1101호~1105호</t>
+          <t>인천광역시 연수구 해돋이로151번길 4 송도동 인피니티타워 502호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://songdo.vandsclinic.co.kr/?channel=4161</t>
+          <t>http://songdoskin.com</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>712</v>
+        <v>350</v>
       </c>
       <c r="Q23" t="n">
-        <v>3860</v>
+        <v>1701</v>
       </c>
       <c r="R23" t="n">
-        <v>4572</v>
+        <v>2051</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2610,17 +2610,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2015039268</t>
+          <t>1990560640</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015039268</t>
+          <t>https://m.place.naver.com/place/1990560640</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2632,29 +2632,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>오운의원 송도점</t>
+          <t>잇츠미성형외과의원</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>shinebeam_songdo@naver.com</t>
+          <t>itsme_clinic_sd@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1644-7427</t>
+          <t>0507-1343-1412</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로197번길 16 리치센트럴 3층 323, 324, 325호</t>
+          <t>인천광역시 연수구 하모니로 158 타임스페이스 A동 5층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://songdo.own-clinic.com</t>
+          <t>https://www.itsmeps.co.kr</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2689,13 +2689,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>569</v>
+        <v>1425</v>
       </c>
       <c r="Q24" t="n">
-        <v>23</v>
+        <v>2255</v>
       </c>
       <c r="R24" t="n">
-        <v>592</v>
+        <v>3680</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2704,17 +2704,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1284197370</t>
+          <t>1123500328</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284197370</t>
+          <t>https://m.place.naver.com/place/1123500328</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2726,29 +2726,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>휴의원</t>
+          <t>오블리브의원 송도</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hueclinic1@naver.com</t>
+          <t>oblivclinic@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1445-2881</t>
+          <t>0507-1350-9120</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 용담로 115</t>
+          <t>인천광역시 연수구 인천타워대로132번길 34 2층, 3층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://www.hue-clinic.com/</t>
+          <t>https://www.obliv.kr/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2758,12 +2758,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>22</v>
+        <v>1401</v>
       </c>
       <c r="Q25" t="n">
-        <v>16</v>
+        <v>2593</v>
       </c>
       <c r="R25" t="n">
-        <v>38</v>
+        <v>3994</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2798,17 +2798,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>11783214</t>
+          <t>1120924408</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11783214</t>
+          <t>https://m.place.naver.com/place/1120924408</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2820,29 +2820,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>리트의원 송도</t>
+          <t>오운의원 송도점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ritclinic_director@naver.com</t>
+          <t>shinebeam_songdo@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>032-833-0107</t>
+          <t>1644-7427</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 테크노파크로111번길 15 401, 402호</t>
+          <t>인천광역시 연수구 인천타워대로197번길 16 리치센트럴 3층 323, 324, 325호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://ritclinic.co.kr</t>
+          <t>https://songdo.own-clinic.com</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2877,13 +2877,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>198</v>
+        <v>572</v>
       </c>
       <c r="Q26" t="n">
-        <v>3414</v>
+        <v>45</v>
       </c>
       <c r="R26" t="n">
-        <v>3612</v>
+        <v>617</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2892,17 +2892,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1410828317</t>
+          <t>1284197370</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1410828317</t>
+          <t>https://m.place.naver.com/place/1284197370</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2914,29 +2914,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>미앤아이의원 송도</t>
+          <t>닥터포유미앤모의원</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>redorange3231@naver.com</t>
+          <t>gabewoon@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>032-862-0075</t>
+          <t>0507-1367-8057</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 69 밀레니엄상가 608호</t>
+          <t>인천광역시 연수구 청능대로 93 이리옴프라자 4층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://sd-meiclinic.co.kr/</t>
+          <t>https://www.instagram.com/drforu_miandmo/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2967,17 +2967,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>211</v>
+        <v>709</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>199</v>
       </c>
       <c r="R27" t="n">
-        <v>216</v>
+        <v>908</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2986,17 +2986,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>20561568</t>
+          <t>13574310</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20561568</t>
+          <t>https://m.place.naver.com/place/13574310</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3008,29 +3008,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>잇츠미성형외과의원</t>
+          <t>제이웰 의원 송도</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>itsme_clinic_sd@naver.com</t>
+          <t>intelligent2862@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1343-1412</t>
+          <t>0507-1372-9700</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 타임스페이스 A동 5층</t>
+          <t>인천광역시 연수구 컨벤시아대로230번길 42 아라프라자 2층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.itsmeps.co.kr</t>
+          <t>http://www.jwellclinic.com</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3065,14 +3065,14 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1414</v>
+        <v>873</v>
       </c>
       <c r="Q28" t="n">
+        <v>1359</v>
+      </c>
+      <c r="R28" t="n">
         <v>2232</v>
       </c>
-      <c r="R28" t="n">
-        <v>3646</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>X</t>
@@ -3080,17 +3080,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1123500328</t>
+          <t>1325901584</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1123500328</t>
+          <t>https://m.place.naver.com/place/1325901584</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3102,43 +3102,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>리더스피부과의원 송도</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>bongpaul@naver.com</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>master@beautyleader.co.kr</t>
-        </is>
-      </c>
+          <t>톡스앤필의원 송도</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>032-715-8190</t>
+          <t>0507-1426-1755</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 194 더샵센트럴파크2차 A동 2층 리더스피부과의원 송도</t>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층 톡스앤필 송도점</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://leaders-sd.com/</t>
+          <t>https://www.toxnfill4.com/</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3163,13 +3155,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>463</v>
+        <v>656</v>
       </c>
       <c r="Q29" t="n">
-        <v>5106</v>
+        <v>5710</v>
       </c>
       <c r="R29" t="n">
-        <v>5569</v>
+        <v>6366</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3178,17 +3170,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1581468228</t>
+          <t>20618221</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581468228</t>
+          <t>https://m.place.naver.com/place/20618221</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3200,29 +3192,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>드림의원</t>
+          <t>미앤아이의원 송도</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>asdream365@naver.com</t>
+          <t>redorange3231@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>032-456-4330</t>
+          <t>032-862-0075</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 청능대로 210 3층</t>
+          <t>인천광역시 연수구 컨벤시아대로 69 밀레니엄상가 608호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://sd-meiclinic.co.kr/</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3232,7 +3224,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3257,13 +3249,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>266</v>
+        <v>211</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3272,17 +3264,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>36476882</t>
+          <t>20561568</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36476882</t>
+          <t>https://m.place.naver.com/place/20561568</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3294,29 +3286,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>맑고고운의원 옥련송도역점</t>
+          <t>플랜유의원</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>value_trend_guide@naver.com</t>
+          <t>xoxozzx@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>032-832-4051</t>
+          <t>0507-1393-9913</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 독배로40번길 11 효명프라자 4층 405호</t>
+          <t>인천광역시 연수구 해돋이로 160-15 송도더퍼스트시티 2층 210호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.pureskinsongdo.co.kr/</t>
+          <t>https://www.planuclinic.co.kr/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3326,7 +3318,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3342,22 +3334,22 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>948</v>
+        <v>1223</v>
       </c>
       <c r="Q31" t="n">
-        <v>50</v>
+        <v>3159</v>
       </c>
       <c r="R31" t="n">
-        <v>998</v>
+        <v>4382</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3366,17 +3358,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1513557735</t>
+          <t>1091669936</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1513557735</t>
+          <t>https://m.place.naver.com/place/1091669936</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3388,24 +3380,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>송도스타피부과의원</t>
+          <t>김운호피부과의원</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sdbenme@naver.com</t>
+          <t>cultfind@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>032-434-2286</t>
+          <t>032-813-9212</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 69 송도 밀레니엄</t>
+          <t>인천광역시 연수구 앵고개로 250 연수메디칼빌딩 3층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3445,13 +3437,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>176</v>
+        <v>1148</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>181</v>
+        <v>1152</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3460,17 +3452,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>20188390</t>
+          <t>13240921</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20188390</t>
+          <t>https://m.place.naver.com/place/13240921</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3482,33 +3474,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>파크뷰의원 송도</t>
+          <t>새로핌피부과의원 인천송도</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>rat3427@naver.com</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>sdparkview83@gmail.com</t>
-        </is>
-      </c>
+          <t>jzvgcz40jz@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>032-710-1404</t>
+          <t>032-833-2777</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 B동 6층</t>
+          <t>인천광역시 연수구 신송로 153 2층 207호~211호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@뷰티의정석-w9e</t>
+          <t>https://serophim.com/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3518,7 +3506,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3543,13 +3531,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>215</v>
+        <v>136</v>
       </c>
       <c r="Q33" t="n">
-        <v>531</v>
+        <v>1602</v>
       </c>
       <c r="R33" t="n">
-        <v>746</v>
+        <v>1738</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3558,17 +3546,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1378532253</t>
+          <t>2049567933</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1378532253</t>
+          <t>https://m.place.naver.com/place/2049567933</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3580,29 +3568,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>유픽의원 송도</t>
+          <t>휴먼피부과의원 송도</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>rkdgkwns43210@naver.com</t>
+          <t>humansdm@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>032-256-6010</t>
+          <t>032-858-3335</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로151번길 4 인피니티타워 6층 601, 602호</t>
+          <t>인천광역시 연수구 센트럴로 263 송도IBS타워 업무동 5층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/upic_clinic_Songdo/</t>
+          <t>http://www.sdhuman.com/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3617,7 +3605,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3628,7 +3616,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3637,13 +3625,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>508</v>
+        <v>1814</v>
       </c>
       <c r="Q34" t="n">
-        <v>5684</v>
+        <v>1540</v>
       </c>
       <c r="R34" t="n">
-        <v>6192</v>
+        <v>3354</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3652,17 +3640,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1794584448</t>
+          <t>36650530</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1794584448</t>
+          <t>https://m.place.naver.com/place/36650530</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3674,44 +3662,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>송도오라클피부과의원</t>
+          <t>연세마이미의원</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>songdo_dermatology@naver.com</t>
+          <t>kti1202@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>032-833-2111</t>
+          <t>032-215-1100</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 6 7층</t>
+          <t>인천광역시 연수구 신송로 166</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://songdo-oracle.com/</t>
+          <t>https://mymii.co.kr/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3722,22 +3710,22 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>809</v>
+        <v>121</v>
       </c>
       <c r="Q35" t="n">
-        <v>1659</v>
+        <v>508</v>
       </c>
       <c r="R35" t="n">
-        <v>2468</v>
+        <v>629</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3746,17 +3734,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1994869691</t>
+          <t>35507465</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994869691</t>
+          <t>https://m.place.naver.com/place/35507465</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3768,29 +3756,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>송도연세피부과의원</t>
+          <t>예쁨의정석의원</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>yonsei-skindoctor@naver.com</t>
+          <t>jungsukbeauty@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1402-0043</t>
+          <t>0507-1371-5609</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로151번길 4 송도동 인피니티타워 502호</t>
+          <t>인천광역시 연수구 랜드마크로 20 상가동 2층 216, 217, 218, 221호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>http://songdoskin.com</t>
+          <t>http://beautyjungsuk.co.kr</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3816,22 +3804,22 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>349</v>
+        <v>94</v>
       </c>
       <c r="Q36" t="n">
-        <v>1824</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>2173</v>
+        <v>99</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3840,17 +3828,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1990560640</t>
+          <t>1141240944</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1990560640</t>
+          <t>https://m.place.naver.com/place/1141240944</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3862,34 +3850,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>변피부과의원</t>
+          <t>밴스의원 송도</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>orangerealtykorea@naver.com</t>
+          <t>mimimomokk@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>032-818-4333</t>
+          <t>032-710-3037</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 원인재로 286 대림아파트 상가 301호</t>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 11층 1101호~1105호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://songdo.vandsclinic.co.kr/?channel=4161</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3910,7 +3898,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3919,13 +3907,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>257</v>
+        <v>709</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>3774</v>
       </c>
       <c r="R37" t="n">
-        <v>262</v>
+        <v>4483</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3934,17 +3922,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>13240993</t>
+          <t>2015039268</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240993</t>
+          <t>https://m.place.naver.com/place/2015039268</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3956,39 +3944,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>필랩의원</t>
+          <t>신피부과의원</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>joung1951@naver.com</t>
+          <t>newskin7582@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-873-0537</t>
+          <t>0507-1405-7583</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 22 GTX센트럴빌딩 C동 6층</t>
+          <t>인천광역시 연수구 신송로 121 센타프라자 7층 704호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://fill-lab.co.kr</t>
+          <t>https://blog.naver.com/newskin7582</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4004,7 +3992,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4013,13 +4001,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1040</v>
+        <v>380</v>
       </c>
       <c r="Q38" t="n">
-        <v>4175</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>5215</v>
+        <v>380</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4028,17 +4016,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1358069959</t>
+          <t>19873520</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358069959</t>
+          <t>https://m.place.naver.com/place/19873520</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4050,38 +4038,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>오네스타의원 송도</t>
+          <t>김지현피부과의원</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>songdobest1@naver.com</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>COPYRIGHT2017@HONESTARC.COM</t>
-        </is>
-      </c>
+          <t>ohhappysmc@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>032-724-8200</t>
+          <t>032-817-8083</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 157 오네스타몰 4층</t>
+          <t>인천광역시 연수구 청능대로 103 4층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://www.honestarc.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4102,22 +4086,22 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1638</v>
+        <v>1041</v>
       </c>
       <c r="Q39" t="n">
-        <v>162</v>
+        <v>10</v>
       </c>
       <c r="R39" t="n">
-        <v>1800</v>
+        <v>1051</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4126,17 +4110,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1824325340</t>
+          <t>13240981</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1824325340</t>
+          <t>https://m.place.naver.com/place/13240981</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4148,34 +4132,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>클렌피부과의원 송도점</t>
+          <t>나다움의원 송도</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>easy_16878@naver.com</t>
+          <t>nadaumclinic@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>032-715-4100</t>
+          <t>032-832-1117</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로230번길 54 송도닥터플러스몰 A동 5층 514-516호</t>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 A동 210-211호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_FWtKC</t>
+          <t>http://www.나다움.com</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4201,17 +4185,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="Q40" t="n">
-        <v>117</v>
+        <v>22</v>
       </c>
       <c r="R40" t="n">
-        <v>480</v>
+        <v>382</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4220,17 +4204,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1983873176</t>
+          <t>1498510198</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1983873176</t>
+          <t>https://m.place.naver.com/place/1498510198</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4242,44 +4226,44 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>피어봄의원 송도</t>
+          <t>신비라인의원 송도</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>pieobom_sd@naver.com</t>
+          <t>shinbilineclinic2@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>032-818-8275</t>
+          <t>0507-1332-7601</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 160 센트럴파크 푸르지오상가 A동 2층 201~207호</t>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 3층 신비라인의원</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://songdo.pieobom.com/</t>
+          <t>http://www.drsinbi.com/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4290,7 +4274,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4299,13 +4283,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>527</v>
+        <v>461</v>
       </c>
       <c r="Q41" t="n">
-        <v>610</v>
+        <v>4512</v>
       </c>
       <c r="R41" t="n">
-        <v>1137</v>
+        <v>4973</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4314,17 +4298,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>37056636</t>
+          <t>12913114</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37056636</t>
+          <t>https://m.place.naver.com/place/12913114</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4336,29 +4320,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>메이린의원 송도</t>
+          <t>휴의원</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>maylin_songdo@naver.com</t>
+          <t>hueclinic1@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1416-8921</t>
+          <t>0507-1445-2881</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 123 현대프리미엄아울렛 송도점 본관 3층</t>
+          <t>인천광역시 연수구 용담로 115</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maylin_clinic_sd/</t>
+          <t>http://www.hue-clinic.com/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4384,22 +4368,22 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>302</v>
+        <v>22</v>
       </c>
       <c r="Q42" t="n">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="R42" t="n">
-        <v>460</v>
+        <v>38</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4408,17 +4392,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1250284461</t>
+          <t>11783214</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1250284461</t>
+          <t>https://m.place.naver.com/place/11783214</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4430,29 +4414,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>신비라인의원 송도</t>
+          <t>알라딘의원</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>shinbilineclinic2@naver.com</t>
+          <t>drjang77@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1332-7601</t>
+          <t>0507-1467-7894</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 3층 신비라인의원</t>
+          <t>인천광역시 연수구 하모니로 158 A동 4층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://www.drsinbi.com/</t>
+          <t>https://blog.naver.com/drjang77</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4467,7 +4451,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4483,17 +4467,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>461</v>
+        <v>158</v>
       </c>
       <c r="Q43" t="n">
-        <v>4421</v>
+        <v>14</v>
       </c>
       <c r="R43" t="n">
-        <v>4882</v>
+        <v>172</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4502,17 +4486,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>12913114</t>
+          <t>1368003991</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12913114</t>
+          <t>https://m.place.naver.com/place/1368003991</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4524,44 +4508,44 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>제이웰 의원 송도</t>
+          <t>메이린의원 송도</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>intelligent2862@naver.com</t>
+          <t>maylin_songdo@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1372-9700</t>
+          <t>0507-1416-8921</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로230번길 42 아라프라자 2층</t>
+          <t>인천광역시 연수구 송도국제대로 123 현대프리미엄아울렛 송도점 본관 3층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://www.jwellclinic.com</t>
+          <t>https://www.instagram.com/maylin_clinic_sd/</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4577,17 +4561,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>869</v>
+        <v>303</v>
       </c>
       <c r="Q44" t="n">
-        <v>1358</v>
+        <v>158</v>
       </c>
       <c r="R44" t="n">
-        <v>2227</v>
+        <v>461</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4596,51 +4580,51 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1325901584</t>
+          <t>1250284461</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1325901584</t>
+          <t>https://m.place.naver.com/place/1250284461</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>피부과</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>하이어마케팅</t>
+          <t>송도스타피부과의원</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>bravoclinic@naver.com</t>
+          <t>sdbenme@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1494-1060</t>
+          <t>032-434-2286</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 313 씨동 2301호</t>
+          <t>인천광역시 연수구 컨벤시아대로 69 송도 밀레니엄</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bravoclinic</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4650,12 +4634,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4675,13 +4659,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4690,17 +4674,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2005191231</t>
+          <t>20188390</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2005191231</t>
+          <t>https://m.place.naver.com/place/20188390</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4712,29 +4696,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>브랜딩로드</t>
+          <t>베룸마케팅</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>branding_road@naver.com</t>
+          <t>verummarketing@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1310-4754</t>
+          <t>0507-1480-3039</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 323 2304-B39호</t>
+          <t>인천광역시 연수구 인천타워대로54번길 15-3 501,502호 알603</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/branding_road</t>
+          <t>https://blog.naver.com/verummarketing</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4769,13 +4753,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4784,17 +4768,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1026515440</t>
+          <t>1164367460</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1026515440</t>
+          <t>https://m.place.naver.com/place/1164367460</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4806,29 +4790,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>베룸마케팅</t>
+          <t>브랜딩로드</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>verummarketing@naver.com</t>
+          <t>branding_road@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1480-3039</t>
+          <t>0507-1310-4754</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로54번길 15-3 501,502호 알603</t>
+          <t>인천광역시 연수구 인천타워대로 323 2304-B39호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/verummarketing</t>
+          <t>https://blog.naver.com/branding_road</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4863,13 +4847,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4878,56 +4862,56 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1164367460</t>
+          <t>1026515440</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1164367460</t>
+          <t>https://m.place.naver.com/place/1026515440</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>기능성화장품</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>코어솔루션</t>
+          <t>하이어마케팅</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>coresolution77@naver.com</t>
+          <t>bravoclinic@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>070-4571-7542</t>
+          <t>0507-1494-1060</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로54번길 3 5층</t>
+          <t>인천광역시 연수구 센트럴로 313 씨동 2301호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://m.livna.kr/</t>
+          <t>https://blog.naver.com/bravoclinic</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4948,12 +4932,12 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -4972,51 +4956,51 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2081756779</t>
+          <t>2005191231</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2081756779</t>
+          <t>https://m.place.naver.com/place/2005191231</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>내과</t>
+          <t>기능성화장품</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>송도탑내과의원</t>
+          <t>코어솔루션</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>read6427@naver.com</t>
+          <t>coresolution77@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>032-719-8089</t>
+          <t>070-4571-7542</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 365 판매시설 A동 305~312호</t>
+          <t>인천광역시 연수구 인천타워대로54번길 3 5층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://www.sdtop.co.kr/</t>
+          <t>https://m.livna.kr/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5031,7 +5015,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5042,22 +5026,22 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>394</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>839</v>
+        <v>0</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5066,17 +5050,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1980900955</t>
+          <t>2081756779</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1980900955</t>
+          <t>https://m.place.naver.com/place/2081756779</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5088,29 +5072,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>송도에이스내과의원</t>
+          <t>송도닥터스의원</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ytonysin@naver.com</t>
+          <t>value_trend_guide@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>032-858-5585</t>
+          <t>032-812-7338</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 415 판매시설동 제2층 제204호, 제207호~211호</t>
+          <t>인천광역시 연수구 송도국제대로 165 홈플러스 송도점 B1F층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ytonysin</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5120,12 +5104,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5145,13 +5129,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>481</v>
+        <v>534</v>
       </c>
       <c r="Q50" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="R50" t="n">
-        <v>580</v>
+        <v>543</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5160,17 +5144,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1311791582</t>
+          <t>37232570</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311791582</t>
+          <t>https://m.place.naver.com/place/37232570</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5182,29 +5166,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>송도닥터스의원</t>
+          <t>송도에이스내과의원</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>value_trend_guide@naver.com</t>
+          <t>ytonysin@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>032-812-7338</t>
+          <t>032-858-5585</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 165 홈플러스 송도점 B1F층</t>
+          <t>인천광역시 연수구 센트럴로 415 판매시설동 제2층 제204호, 제207호~211호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ytonysin</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5214,12 +5198,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5239,13 +5223,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>534</v>
+        <v>487</v>
       </c>
       <c r="Q51" t="n">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="R51" t="n">
-        <v>543</v>
+        <v>591</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5254,61 +5238,61 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>37232570</t>
+          <t>1311791582</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37232570</t>
+          <t>https://m.place.naver.com/place/1311791582</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>병원,의원</t>
+          <t>내과</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>피앤비의원</t>
+          <t>송도탑내과의원</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>pnb_communication@naver.com</t>
+          <t>read6427@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>032-832-2251</t>
+          <t>032-719-8089</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 한진로 23 로얄프라자</t>
+          <t>인천광역시 연수구 인천타워대로 365 판매시설 A동 305~312호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.sdtop.co.kr/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5333,13 +5317,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>198</v>
+        <v>451</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>395</v>
       </c>
       <c r="R52" t="n">
-        <v>199</v>
+        <v>846</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5348,17 +5332,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>13241044</t>
+          <t>1980900955</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13241044</t>
+          <t>https://m.place.naver.com/place/1980900955</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5370,24 +5354,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>현대성모의원</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>eungbo14@naver.com</t>
-        </is>
-      </c>
+          <t>피앤비의원</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>032-816-1367</t>
+          <t>032-832-2251</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 함박뫼로 28</t>
+          <t>인천광역시 연수구 한진로 23 로얄프라자</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5427,13 +5407,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>161</v>
+        <v>199</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5442,51 +5422,47 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>13240955</t>
+          <t>13241044</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240955</t>
+          <t>https://m.place.naver.com/place/13241044</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>비뇨의학과</t>
+          <t>병원,의원</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>유쾌한비뇨의학과의원 송도점</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>uroskin_sd@naver.com</t>
-        </is>
-      </c>
+          <t>현대성모의원</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>032-831-8575</t>
+          <t>032-816-1367</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 153 더마란츠타워 304호,305호</t>
+          <t>인천광역시 연수구 함박뫼로 28</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://enjoyuro.com/v2/s01/sub02_5.php</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5496,7 +5472,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5521,13 +5497,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>307</v>
+        <v>160</v>
       </c>
       <c r="Q54" t="n">
-        <v>4189</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>4496</v>
+        <v>161</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5536,51 +5512,51 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1214184965</t>
+          <t>13240955</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1214184965</t>
+          <t>https://m.place.naver.com/place/13240955</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>성형외과</t>
+          <t>비뇨의학과</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>골드리버의원 인천 송도</t>
+          <t>유쾌한비뇨의학과의원 송도점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>songdo_goldriver@naver.com</t>
+          <t>uroskin_sd@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1433-5356</t>
+          <t>032-831-8575</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로130번길 14 3층 305호</t>
+          <t>인천광역시 연수구 신송로 153 더마란츠타워 304호,305호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/songdo_goldriver</t>
+          <t>http://enjoyuro.com/v2/s01/sub02_5.php</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5595,7 +5571,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5611,17 +5587,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>242</v>
+        <v>307</v>
       </c>
       <c r="Q55" t="n">
-        <v>579</v>
+        <v>4182</v>
       </c>
       <c r="R55" t="n">
-        <v>821</v>
+        <v>4489</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5630,17 +5606,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>37647473</t>
+          <t>1214184965</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37647473</t>
+          <t>https://m.place.naver.com/place/1214184965</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5652,29 +5628,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JK위드미의원</t>
+          <t>송도 리앤스타의원</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>withme5401@naver.com</t>
+          <t>sdbenme@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1402-7991</t>
+          <t>0507-1484-5030</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 165 포스코타워송도 6층 jk위드미의원</t>
+          <t>인천광역시 연수구 센트럴로 160 송도 푸르지오 주상복합 C동 상가 2층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://jk-withme.com/</t>
+          <t>https://songdo-leenstar.com/</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5689,7 +5665,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5709,13 +5685,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>698</v>
+        <v>726</v>
       </c>
       <c r="Q56" t="n">
-        <v>666</v>
+        <v>68</v>
       </c>
       <c r="R56" t="n">
-        <v>1364</v>
+        <v>794</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5724,17 +5700,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>37485848</t>
+          <t>1114619038</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37485848</t>
+          <t>https://m.place.naver.com/place/1114619038</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5746,29 +5722,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>앤의원 인천연수점</t>
+          <t>JK위드미의원</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>annds@naver.com</t>
+          <t>withme5401@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1436-9703</t>
+          <t>0507-1402-7991</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 앵고개로264번길 30-4 영남프라자 3층 앤피부과성형외과</t>
+          <t>인천광역시 연수구 컨벤시아대로 165 포스코타워송도 6층 jk위드미의원</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://annincheon.com/</t>
+          <t>http://jk-withme.com/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5803,13 +5779,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1095</v>
+        <v>697</v>
       </c>
       <c r="Q57" t="n">
-        <v>128</v>
+        <v>666</v>
       </c>
       <c r="R57" t="n">
-        <v>1223</v>
+        <v>1363</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5818,17 +5794,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>20370288</t>
+          <t>37485848</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20370288</t>
+          <t>https://m.place.naver.com/place/37485848</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5840,34 +5816,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>안녕성형외과의원</t>
+          <t>골드리버의원 인천 송도</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>hellops5400@naver.com</t>
+          <t>songdo_goldriver@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>032-858-5400</t>
+          <t>0507-1433-5356</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 송도에스원타워 3층</t>
+          <t>인천광역시 연수구 컨벤시아대로130번길 14 3층 305호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://www.hellops.co.kr</t>
+          <t>https://blog.naver.com/songdo_goldriver</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5877,7 +5853,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5897,13 +5873,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3261</v>
+        <v>242</v>
       </c>
       <c r="Q58" t="n">
-        <v>342</v>
+        <v>572</v>
       </c>
       <c r="R58" t="n">
-        <v>3603</v>
+        <v>814</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5912,17 +5888,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1059884727</t>
+          <t>37647473</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1059884727</t>
+          <t>https://m.place.naver.com/place/37647473</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5934,29 +5910,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>송도 리앤스타의원</t>
+          <t>앤의원 인천연수점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sdbenme@naver.com</t>
+          <t>annds@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1484-5030</t>
+          <t>0507-1436-9703</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 160 송도 푸르지오 주상복합 C동 상가 2층</t>
+          <t>인천광역시 연수구 앵고개로264번길 30-4 영남프라자 3층 앤피부과성형외과</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://songdo-leenstar.com/</t>
+          <t>https://annincheon.com/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5971,7 +5947,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5991,13 +5967,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>714</v>
+        <v>1096</v>
       </c>
       <c r="Q59" t="n">
-        <v>65</v>
+        <v>131</v>
       </c>
       <c r="R59" t="n">
-        <v>779</v>
+        <v>1227</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6006,51 +5982,51 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1114619038</t>
+          <t>20370288</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1114619038</t>
+          <t>https://m.place.naver.com/place/20370288</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>소아청소년과</t>
+          <t>성형외과</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>송도맘편한소아청소년과의원</t>
+          <t>안녕성형외과의원</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>dransehwan@naver.com</t>
+          <t>hellops5400@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1485-1365</t>
+          <t>032-858-5400</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 68 2층 204호~207호, 252호, 255호~257호</t>
+          <t>인천광역시 연수구 해돋이로 168-2 송도에스원타워 3층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://www.momsoa.co.kr</t>
+          <t>http://www.hellops.co.kr</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6060,12 +6036,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6076,22 +6052,22 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>786</v>
+        <v>3286</v>
       </c>
       <c r="Q60" t="n">
-        <v>179</v>
+        <v>346</v>
       </c>
       <c r="R60" t="n">
-        <v>965</v>
+        <v>3632</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6100,17 +6076,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1214392802</t>
+          <t>1059884727</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1214392802</t>
+          <t>https://m.place.naver.com/place/1059884727</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6122,29 +6098,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>브이아이씨소아청소년과의원</t>
+          <t>송도맘편한소아청소년과의원</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>vic365i@naver.com</t>
+          <t>dransehwan@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1407-1406</t>
+          <t>0507-1485-1365</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 157 오네스타 7층</t>
+          <t>인천광역시 연수구 랜드마크로 68 2층 204호~207호, 252호, 255호~257호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://www.vic365i.com</t>
+          <t>http://www.momsoa.co.kr</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6154,7 +6130,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6170,22 +6146,22 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1728</v>
+        <v>789</v>
       </c>
       <c r="Q61" t="n">
-        <v>872</v>
+        <v>186</v>
       </c>
       <c r="R61" t="n">
-        <v>2600</v>
+        <v>975</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6194,61 +6170,61 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1265073798</t>
+          <t>1214392802</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1265073798</t>
+          <t>https://m.place.naver.com/place/1214392802</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>이비인후과</t>
+          <t>소아청소년과</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>삼성드림이비인후과의원 인천송도</t>
+          <t>브이아이씨소아청소년과의원</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kjssdream@naver.com</t>
+          <t>vic365i@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1400-0365</t>
+          <t>0507-1407-1406</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 232 더샵센트럴파크1차 E동 2층 220호</t>
+          <t>인천광역시 연수구 송도국제대로 157 오네스타 7층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>http://www.ssdream.co.kr/</t>
+          <t>http://www.vic365i.com</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6264,7 +6240,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6273,13 +6249,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>647</v>
+        <v>1727</v>
       </c>
       <c r="Q62" t="n">
-        <v>853</v>
+        <v>876</v>
       </c>
       <c r="R62" t="n">
-        <v>1500</v>
+        <v>2603</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6288,61 +6264,61 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1576664853</t>
+          <t>1265073798</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1576664853</t>
+          <t>https://m.place.naver.com/place/1265073798</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>이비인후과</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>엘에스디자인그룹</t>
+          <t>삼성드림이비인후과의원 인천송도</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>lsdesign3993@naver.com</t>
+          <t>kjssdream@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1435-3928</t>
+          <t>0507-1400-0365</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도미래로 30 송도 BRC 스마트밸리 E동</t>
+          <t>인천광역시 연수구 센트럴로 232 더샵센트럴파크1차 E동 2층 220호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lsdesign3993</t>
+          <t>http://www.ssdream.co.kr/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6358,22 +6334,22 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>876</v>
       </c>
       <c r="R63" t="n">
-        <v>1</v>
+        <v>1525</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6382,61 +6358,61 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>21905049</t>
+          <t>1576664853</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21905049</t>
+          <t>https://m.place.naver.com/place/1576664853</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>정형외과</t>
+          <t>인테리어디자인</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>벗정형외과의원 송도</t>
+          <t>엘에스디자인그룹</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>srangb@naver.com</t>
+          <t>lsdesign3993@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1379-7917</t>
+          <t>0507-1435-3928</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 6 송도중앙타워 8층</t>
+          <t>인천광역시 연수구 송도미래로 30 송도 BRC 스마트밸리 E동</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://friendos.co.kr/</t>
+          <t>https://blog.naver.com/lsdesign3993</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6461,13 +6437,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>803</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>1098</v>
+        <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>1901</v>
+        <v>1</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6476,17 +6452,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1925923703</t>
+          <t>21905049</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1925923703</t>
+          <t>https://m.place.naver.com/place/21905049</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6498,29 +6474,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>청담해리슨송도병원</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>harrison_songdo@naver.com</t>
-        </is>
-      </c>
+          <t>벗정형외과의원 송도</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>032-832-5488</t>
+          <t>0507-1379-7917</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 157-9 3~8층</t>
+          <t>인천광역시 연수구 하모니로178번길 6 송도중앙타워 8층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>http://harrisonsongdo.com/main.php</t>
+          <t>https://friendos.co.kr/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6551,17 +6523,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>653</v>
+        <v>813</v>
       </c>
       <c r="Q65" t="n">
-        <v>1238</v>
+        <v>1253</v>
       </c>
       <c r="R65" t="n">
-        <v>1891</v>
+        <v>2066</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6570,17 +6542,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1077150743</t>
+          <t>1925923703</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1077150743</t>
+          <t>https://m.place.naver.com/place/1925923703</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6592,39 +6564,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>송도 탑 정형외과의원</t>
+          <t>청담해리슨송도병원</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>songdo-top@naver.com</t>
+          <t>harrison_songdo@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1440-6767</t>
+          <t>032-832-5488</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 261 GS슈퍼마켓 2층</t>
+          <t>인천광역시 연수구 신송로 157-9 3~8층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/songdo-top</t>
+          <t>http://harrisonsongdo.com/main.php</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6645,17 +6617,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1031</v>
+        <v>661</v>
       </c>
       <c r="Q66" t="n">
-        <v>2957</v>
+        <v>1243</v>
       </c>
       <c r="R66" t="n">
-        <v>3988</v>
+        <v>1904</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6664,17 +6636,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1927029254</t>
+          <t>1077150743</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1927029254</t>
+          <t>https://m.place.naver.com/place/1077150743</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6743,13 +6715,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>4469</v>
+        <v>4508</v>
       </c>
       <c r="Q67" t="n">
-        <v>2152</v>
+        <v>2091</v>
       </c>
       <c r="R67" t="n">
-        <v>6621</v>
+        <v>6599</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6768,41 +6740,41 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>한방병원</t>
+          <t>정형외과</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>자양한방병원 인천 송도</t>
+          <t>송도 탑 정형외과의원</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jayangpr@naver.com</t>
+          <t>songdo-top@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>032-255-1000</t>
+          <t>0507-1440-6767</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 154 더제니스 4층</t>
+          <t>인천광역시 연수구 송도국제대로 261 GS슈퍼마켓 2층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://www.jayanghospital.co.kr</t>
+          <t>https://blog.naver.com/songdo-top</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6833,17 +6805,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>970</v>
+        <v>1019</v>
       </c>
       <c r="Q68" t="n">
-        <v>1791</v>
+        <v>2960</v>
       </c>
       <c r="R68" t="n">
-        <v>2761</v>
+        <v>3979</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6852,17 +6824,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1788145600</t>
+          <t>1927029254</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1788145600</t>
+          <t>https://m.place.naver.com/place/1927029254</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6934,10 +6906,10 @@
         <v>174</v>
       </c>
       <c r="Q69" t="n">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="R69" t="n">
-        <v>934</v>
+        <v>946</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6956,41 +6928,41 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>한의원</t>
+          <t>한방병원</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>365송도경희한의원</t>
+          <t>자양한방병원 인천 송도</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>songdokh@naver.com</t>
+          <t>jayangpr@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1397-8576</t>
+          <t>032-255-1000</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 415 상가동 250호, 251호</t>
+          <t>인천광역시 연수구 신송로 154 더제니스 4층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/songdokh</t>
+          <t>http://www.jayanghospital.co.kr</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -7025,13 +6997,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2418</v>
+        <v>974</v>
       </c>
       <c r="Q70" t="n">
-        <v>2393</v>
+        <v>1633</v>
       </c>
       <c r="R70" t="n">
-        <v>4811</v>
+        <v>2607</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7040,17 +7012,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1457517308</t>
+          <t>1788145600</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1457517308</t>
+          <t>https://m.place.naver.com/place/1788145600</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7119,13 +7091,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="Q71" t="n">
-        <v>2708</v>
+        <v>2761</v>
       </c>
       <c r="R71" t="n">
-        <v>3220</v>
+        <v>3275</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7144,7 +7116,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7156,34 +7128,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>나은내일한의원 인천 송도</t>
+          <t>울림한의원</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>lunarmix@naver.com</t>
+          <t>woolimkmd@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1445-9252</t>
+          <t>0507-1308-3652</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 153 더 마란츠타워 8층</t>
+          <t>인천광역시 연수구 해돋이로 168-2 에스원타워 307호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.naunmed.com/?utm_source=naver&amp;amp;utm_medium=place</t>
+          <t>https://blog.naver.com/woolimkmd</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7204,7 +7176,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7213,13 +7185,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>581</v>
+        <v>289</v>
       </c>
       <c r="Q72" t="n">
-        <v>3583</v>
+        <v>2587</v>
       </c>
       <c r="R72" t="n">
-        <v>4164</v>
+        <v>2876</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7228,17 +7200,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1695745929</t>
+          <t>1002218506</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695745929</t>
+          <t>https://m.place.naver.com/place/1002218506</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7250,29 +7222,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>울림한의원</t>
+          <t>소통부부한의원 송도</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>woolimkmd@naver.com</t>
+          <t>qwlukw26@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1308-3652</t>
+          <t>0507-1422-3425</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 에스원타워 307호</t>
+          <t>인천광역시 연수구 신송로 164 5층 501호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woolimkmd</t>
+          <t>http://www.sotongbooboo-songdo.co.kr</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7287,7 +7259,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7307,13 +7279,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>289</v>
+        <v>1079</v>
       </c>
       <c r="Q73" t="n">
-        <v>2569</v>
+        <v>2287</v>
       </c>
       <c r="R73" t="n">
-        <v>2858</v>
+        <v>3366</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7322,17 +7294,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1002218506</t>
+          <t>1437757765</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1002218506</t>
+          <t>https://m.place.naver.com/place/1437757765</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7344,29 +7316,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>인천송도 더율한의원</t>
+          <t>자윤한의원 인천송도점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>hansister82@naver.com</t>
+          <t>nuk37@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1432-1075</t>
+          <t>032-721-8200</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 4층 403호</t>
+          <t>인천광역시 연수구 신송로 153 더마란츠 6층 자윤한의원 인천송도점</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hansister82</t>
+          <t>http://i-jayoon.co.kr/sd</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7392,7 +7364,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7401,13 +7373,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2213</v>
+        <v>171</v>
       </c>
       <c r="Q74" t="n">
-        <v>5301</v>
+        <v>6116</v>
       </c>
       <c r="R74" t="n">
-        <v>7514</v>
+        <v>6287</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7416,17 +7388,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>36459284</t>
+          <t>1449901613</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36459284</t>
+          <t>https://m.place.naver.com/place/1449901613</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7438,29 +7410,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>자윤한의원 인천송도점</t>
+          <t>365송도경희한의원</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>nuk37@naver.com</t>
+          <t>songdokh@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>032-721-8200</t>
+          <t>0507-1397-8576</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 153 더마란츠 6층 자윤한의원 인천송도점</t>
+          <t>인천광역시 연수구 센트럴로 415 상가동 250호, 251호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://i-jayoon.co.kr/sd</t>
+          <t>https://blog.naver.com/songdokh</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7470,7 +7442,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7486,7 +7458,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7495,13 +7467,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>169</v>
+        <v>2426</v>
       </c>
       <c r="Q75" t="n">
-        <v>6538</v>
+        <v>2343</v>
       </c>
       <c r="R75" t="n">
-        <v>6707</v>
+        <v>4769</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7510,17 +7482,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1449901613</t>
+          <t>1457517308</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1449901613</t>
+          <t>https://m.place.naver.com/place/1457517308</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7532,34 +7504,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>소통부부한의원 송도</t>
+          <t>나은내일한의원 인천 송도</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>qwlukw26@naver.com</t>
+          <t>lunarmix@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1422-3425</t>
+          <t>0507-1445-9252</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 164 5층 501호</t>
+          <t>인천광역시 연수구 신송로 153 더 마란츠타워 8층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://www.sotongbooboo-songdo.co.kr</t>
+          <t>https://www.naunmed.com/?utm_source=naver&amp;amp;utm_medium=place</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7569,7 +7541,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7580,7 +7552,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7589,13 +7561,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1073</v>
+        <v>590</v>
       </c>
       <c r="Q76" t="n">
-        <v>2300</v>
+        <v>3645</v>
       </c>
       <c r="R76" t="n">
-        <v>3373</v>
+        <v>4235</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7604,17 +7576,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1437757765</t>
+          <t>1695745929</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1437757765</t>
+          <t>https://m.place.naver.com/place/1695745929</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_derma/송도_피부과.xlsx
+++ b/naver-place-crawler/results_derma/송도_피부과.xlsx
@@ -564,33 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>파크뷰의원 송도</t>
+          <t>피즈벨머의원</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rat3427@naver.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>nsdparkview83@gmail.com</t>
-        </is>
-      </c>
+          <t>psbellment@naver.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>032-710-1404</t>
+          <t>0507-1319-6862</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 B동 6층</t>
+          <t>인천광역시 연수구 해돋이로 160-14 301호~304호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@뷰티의정석-w9e</t>
+          <t>https://psbellment.com/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -605,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -616,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="Q2" t="n">
-        <v>539</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>756</v>
+        <v>14</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1378532253</t>
+          <t>2036564067</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1378532253</t>
+          <t>https://m.place.naver.com/place/2036564067</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -662,38 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>리더스피부과의원 송도</t>
+          <t>예쁨의정석의원</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bongpaul@naver.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>master@beautyleader.co.kr</t>
-        </is>
-      </c>
+          <t>jungsukbeauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>032-715-8190</t>
+          <t>0507-1371-5609</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 194 더샵센트럴파크2차 A동 2층 리더스피부과의원 송도</t>
+          <t>인천광역시 연수구 랜드마크로 20 상가동 2층 216, 217, 218, 221호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://leaders-sd.com/</t>
+          <t>http://beautyjungsuk.co.kr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -714,22 +706,22 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>464</v>
+        <v>94</v>
       </c>
       <c r="Q3" t="n">
-        <v>4812</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>5276</v>
+        <v>99</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1581468228</t>
+          <t>1141240944</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581468228</t>
+          <t>https://m.place.naver.com/place/1141240944</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -760,26 +752,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>드림피부과</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>오네스타의원 송도</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>songdobest1@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>COPYRIGHT2017@HONESTARC.COM</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>032-724-8200</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 청능대로 210 스퀘어원</t>
+          <t>인천광역시 연수구 송도국제대로 157 오네스타몰 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.honestarc.com</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -800,22 +804,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1639</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1801</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>4170845550</t>
+          <t>1824325340</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/4170845550</t>
+          <t>https://m.place.naver.com/place/1824325340</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -846,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>변피부과의원</t>
+          <t>필랩의원</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>orangerealtykorea@naver.com</t>
+          <t>joung1951@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>032-818-4333</t>
+          <t>0507-873-0537</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 원인재로 286 대림아파트 상가 301호</t>
+          <t>인천광역시 연수구 하모니로178번길 22 GTX센트럴빌딩 C동 6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://fill-lab.co.kr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +882,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>257</v>
+        <v>1039</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>4381</v>
       </c>
       <c r="R5" t="n">
-        <v>262</v>
+        <v>5420</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13240993</t>
+          <t>1358069959</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240993</t>
+          <t>https://m.place.naver.com/place/1358069959</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -940,44 +944,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>실버라이닝의원</t>
+          <t>신피부과의원</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>silver_lining_songdo@naver.com</t>
+          <t>newskin7582@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1465-8112</t>
+          <t>0507-1405-7583</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-15 제2층 제201호~제205호</t>
+          <t>인천광역시 연수구 신송로 121 센타프라자 7층 704호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://silverlining.clinic</t>
+          <t>https://blog.naver.com/newskin7582</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -988,22 +992,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>194</v>
+        <v>380</v>
       </c>
       <c r="Q6" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>427</v>
+        <v>380</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1081885317</t>
+          <t>19873520</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1081885317</t>
+          <t>https://m.place.naver.com/place/19873520</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>맑고고운시그니처의원 인천연수동춘점</t>
+          <t>오운의원 송도점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pinkclean0713@naver.com</t>
+          <t>shinebeam_songdo@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1497-1523</t>
+          <t>1644-7427</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 먼우금로 88 5층 501, 502호</t>
+          <t>인천광역시 연수구 인천타워대로197번길 16 리치센트럴 3층 323, 324, 325호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.incheonsignature.com/</t>
+          <t>https://songdo.own-clinic.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,7 +1070,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1091,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>277</v>
+        <v>579</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="R7" t="n">
-        <v>282</v>
+        <v>625</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1037963149</t>
+          <t>1284197370</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037963149</t>
+          <t>https://m.place.naver.com/place/1284197370</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1128,25 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>미소지움피부과의원</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>나다움의원 송도</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>nadaumclinic@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>032-832-7775</t>
+          <t>032-832-1117</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 69 송도밀레니엄 509호</t>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 A동 210-211호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.misoskin.com</t>
+          <t>http://www.나다움.com</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1172,22 +1180,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>738</v>
+        <v>362</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="R8" t="n">
-        <v>748</v>
+        <v>385</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>20393004</t>
+          <t>1498510198</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20393004</t>
+          <t>https://m.place.naver.com/place/1498510198</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1218,34 +1226,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>맑고고운의원 옥련송도역점</t>
+          <t>신비라인의원 송도</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>value_trend_guide@naver.com</t>
+          <t>shinbilineclinic2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>032-832-4051</t>
+          <t>0507-1332-7601</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 독배로40번길 11 효명프라자 4층 405호</t>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 3층 신비라인의원</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.pureskinsongdo.co.kr/</t>
+          <t>http://www.drsinbi.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1255,7 +1263,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1271,17 +1279,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>948</v>
+        <v>461</v>
       </c>
       <c r="Q9" t="n">
-        <v>50</v>
+        <v>4574</v>
       </c>
       <c r="R9" t="n">
-        <v>998</v>
+        <v>5035</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1513557735</t>
+          <t>12913114</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1513557735</t>
+          <t>https://m.place.naver.com/place/12913114</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1312,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>유픽의원 송도</t>
+          <t>미소지움피부과의원</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rkdgkwns43210@naver.com</t>
+          <t>aaprettygirl@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>032-256-6010</t>
+          <t>032-832-7775</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로151번길 4 인피니티타워 6층 601, 602호</t>
+          <t>인천광역시 연수구 컨벤시아대로 69 송도밀레니엄 509호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/upic_clinic_Songdo/</t>
+          <t>http://www.misoskin.com</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1365,17 +1373,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>510</v>
+        <v>738</v>
       </c>
       <c r="Q10" t="n">
-        <v>5015</v>
+        <v>10</v>
       </c>
       <c r="R10" t="n">
-        <v>5525</v>
+        <v>748</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1794584448</t>
+          <t>20393004</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1794584448</t>
+          <t>https://m.place.naver.com/place/20393004</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1406,29 +1414,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>피어봄의원 송도</t>
+          <t>아리엘의원 송도</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pieobom_sd@naver.com</t>
+          <t>clinicariel@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>032-818-8275</t>
+          <t>0507-1413-3303</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 160 센트럴파크 푸르지오상가 A동 2층 201~207호</t>
+          <t>인천광역시 연수구 컨벤시아대로130번길 14 플러스메디타워 4층 1, 2, 3, 4, 5호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://songdo.pieobom.com/</t>
+          <t>https://arielclinickorea.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1459,17 +1467,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>531</v>
+        <v>319</v>
       </c>
       <c r="Q11" t="n">
-        <v>614</v>
+        <v>5882</v>
       </c>
       <c r="R11" t="n">
-        <v>1145</v>
+        <v>6201</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>37056636</t>
+          <t>1024929142</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37056636</t>
+          <t>https://m.place.naver.com/place/1024929142</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1500,29 +1508,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>클렌피부과의원 송도점</t>
+          <t>송도연세피부과의원</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>easy_16878@naver.com</t>
+          <t>yonsei-skindoctor@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>032-715-4100</t>
+          <t>0507-1402-0043</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로230번길 54 송도닥터플러스몰 A동 5층 514-516호</t>
+          <t>인천광역시 연수구 해돋이로151번길 4 송도동 인피니티타워 502호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_FWtKC</t>
+          <t>http://songdoskin.com</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1532,12 +1540,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1553,17 +1561,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="Q12" t="n">
-        <v>117</v>
+        <v>1704</v>
       </c>
       <c r="R12" t="n">
-        <v>484</v>
+        <v>2054</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1580,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1983873176</t>
+          <t>1990560640</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1983873176</t>
+          <t>https://m.place.naver.com/place/1990560640</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1594,39 +1602,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>송도오라클피부과의원</t>
+          <t>에피움의원</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>songdo_dermatology@naver.com</t>
+          <t>epium@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>032-833-2111</t>
+          <t>0507-1386-9979</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 6 7층</t>
+          <t>인천광역시 연수구 송도과학로16번길 33-3 C동 2층 207호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://songdo-oracle.com/</t>
+          <t>https://epium.kr</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1642,22 +1650,22 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>819</v>
+        <v>357</v>
       </c>
       <c r="Q13" t="n">
-        <v>1804</v>
+        <v>1984</v>
       </c>
       <c r="R13" t="n">
-        <v>2623</v>
+        <v>2341</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,17 +1674,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1994869691</t>
+          <t>2033501340</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1994869691</t>
+          <t>https://m.place.naver.com/place/2033501340</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1688,39 +1696,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>피즈벨머의원</t>
+          <t>제이웰 의원 송도</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>psbellment@naver.com</t>
+          <t>intelligent2862@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1319-6862</t>
+          <t>0507-1372-9700</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-14 301호~304호</t>
+          <t>인천광역시 연수구 컨벤시아대로230번길 42 아라프라자 2층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/psbellment</t>
+          <t>http://www.jwellclinic.com</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1736,7 +1744,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1745,13 +1753,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>879</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1364</v>
       </c>
       <c r="R14" t="n">
-        <v>14</v>
+        <v>2243</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,17 +1768,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2036564067</t>
+          <t>1325901584</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036564067</t>
+          <t>https://m.place.naver.com/place/1325901584</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1782,44 +1790,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아리엘의원 송도</t>
+          <t>미앤아이의원 송도</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>clinicariel@naver.com</t>
+          <t>redorange3231@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1413-3303</t>
+          <t>032-862-0075</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로130번길 14 플러스메디타워 4층 1, 2, 3, 4, 5호</t>
+          <t>인천광역시 연수구 컨벤시아대로 69 밀레니엄상가 608호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://arielclinickorea.com/</t>
+          <t>http://sd-meiclinic.co.kr/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1830,7 +1838,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1839,13 +1847,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>320</v>
+        <v>211</v>
       </c>
       <c r="Q15" t="n">
-        <v>5870</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>6190</v>
+        <v>216</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,17 +1862,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1024929142</t>
+          <t>20561568</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024929142</t>
+          <t>https://m.place.naver.com/place/20561568</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1876,29 +1884,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>리겐의원 송도</t>
+          <t>오블리브의원 송도</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>songdo_st@naver.com</t>
+          <t>oblivclinic@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1470-1351</t>
+          <t>0507-1350-9120</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로152번길 9 8층</t>
+          <t>인천광역시 연수구 인천타워대로132번길 34 2층, 3층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://www.regainclinic.co.kr</t>
+          <t>https://www.obliv.kr/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1924,7 +1932,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1933,13 +1941,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>419</v>
+        <v>1418</v>
       </c>
       <c r="Q16" t="n">
-        <v>135</v>
+        <v>2599</v>
       </c>
       <c r="R16" t="n">
-        <v>554</v>
+        <v>4017</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,17 +1956,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1724640605</t>
+          <t>1120924408</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1724640605</t>
+          <t>https://m.place.naver.com/place/1120924408</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1970,29 +1978,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>닥터에버스의원 송도</t>
+          <t>타토아의원 인천송도</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dreverssd03@naver.com</t>
+          <t>brandbondam@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1360-7570</t>
+          <t>0507-1333-7210</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 165-17 월드메르디앙 2층</t>
+          <t>인천광역시 연수구 컨벤시아대로 69 202호, 203호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://evers17.co.kr/</t>
+          <t>https://tatoasd.co.kr/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2027,13 +2035,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>597</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1364</v>
+        <v>1</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,17 +2050,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1614509215</t>
+          <t>2074149288</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1614509215</t>
+          <t>https://m.place.naver.com/place/2074149288</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2064,34 +2072,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>리트의원 송도</t>
+          <t>톡스앤필의원 송도</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ritclinic_director@naver.com</t>
+          <t>joung1951@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>032-833-0107</t>
+          <t>0507-1426-1755</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 테크노파크로111번길 15 401, 402호</t>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층 톡스앤필 송도점</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://ritclinic.co.kr</t>
+          <t>https://www.toxnfill4.com/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2121,13 +2129,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>201</v>
+        <v>659</v>
       </c>
       <c r="Q18" t="n">
-        <v>2711</v>
+        <v>5750</v>
       </c>
       <c r="R18" t="n">
-        <v>2912</v>
+        <v>6409</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,17 +2144,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1410828317</t>
+          <t>20618221</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1410828317</t>
+          <t>https://m.place.naver.com/place/20618221</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2158,48 +2166,44 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>오네스타의원 송도</t>
+          <t>알라딘의원</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>songdobest1@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>COPYRIGHT2017@HONESTARC.COM</t>
-        </is>
-      </c>
+          <t>drjang77@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>032-724-8200</t>
+          <t>0507-1467-7894</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 157 오네스타몰 4층</t>
+          <t>인천광역시 연수구 하모니로 158 A동 4층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://www.honestarc.com</t>
+          <t>https://blog.naver.com/drjang77</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2210,22 +2214,22 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1634</v>
+        <v>158</v>
       </c>
       <c r="Q19" t="n">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="R19" t="n">
-        <v>1796</v>
+        <v>172</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2234,17 +2238,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1824325340</t>
+          <t>1368003991</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1824325340</t>
+          <t>https://m.place.naver.com/place/1368003991</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2256,34 +2260,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>필랩의원</t>
+          <t>리더스피부과의원 송도</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>joung1951@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>bongpaul@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>master@beautyleader.co.kr</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-873-0537</t>
+          <t>032-715-8190</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 22 GTX센트럴빌딩 C동 6층</t>
+          <t>인천광역시 연수구 센트럴로 194 더샵센트럴파크2차 A동 2층 리더스피부과의원 송도</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://fill-lab.co.kr</t>
+          <t>https://leaders-sd.com/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2309,17 +2317,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1040</v>
+        <v>464</v>
       </c>
       <c r="Q20" t="n">
-        <v>4285</v>
+        <v>4881</v>
       </c>
       <c r="R20" t="n">
-        <v>5325</v>
+        <v>5345</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2328,17 +2336,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1358069959</t>
+          <t>1581468228</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358069959</t>
+          <t>https://m.place.naver.com/place/1581468228</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2350,44 +2358,44 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>에피움의원</t>
+          <t>맑고고운의원 옥련송도역점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>epium@naver.com</t>
+          <t>value_trend_guide@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>032-818-9979</t>
+          <t>032-832-4051</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로16번길 33-3 C동 2층 207호</t>
+          <t>인천광역시 연수구 독배로40번길 11 효명프라자 4층 405호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://epium.kr</t>
+          <t>https://www.pureskinsongdo.co.kr/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2398,7 +2406,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2407,13 +2415,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>349</v>
+        <v>948</v>
       </c>
       <c r="Q21" t="n">
-        <v>1898</v>
+        <v>50</v>
       </c>
       <c r="R21" t="n">
-        <v>2247</v>
+        <v>998</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2422,17 +2430,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2033501340</t>
+          <t>1513557735</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033501340</t>
+          <t>https://m.place.naver.com/place/1513557735</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2444,24 +2452,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>드림의원</t>
+          <t>김지현피부과의원</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>asdream365@naver.com</t>
+          <t>ohhappysmc@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>032-456-4330</t>
+          <t>032-817-8083</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 청능대로 210 3층</t>
+          <t>인천광역시 연수구 청능대로 103 4층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2501,13 +2509,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>266</v>
+        <v>1042</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R22" t="n">
-        <v>268</v>
+        <v>1052</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2516,17 +2524,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>36476882</t>
+          <t>13240981</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36476882</t>
+          <t>https://m.place.naver.com/place/13240981</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2538,44 +2546,44 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>송도연세피부과의원</t>
+          <t>닥터포유미앤모의원</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>yonsei-skindoctor@naver.com</t>
+          <t>gabewoon@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1402-0043</t>
+          <t>0507-1367-8057</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로151번길 4 송도동 인피니티타워 502호</t>
+          <t>인천광역시 연수구 청능대로 93 이리옴프라자 4층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://songdoskin.com</t>
+          <t>https://www.instagram.com/drforu_miandmo/</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2586,7 +2594,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2595,13 +2603,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>350</v>
+        <v>709</v>
       </c>
       <c r="Q23" t="n">
-        <v>1701</v>
+        <v>200</v>
       </c>
       <c r="R23" t="n">
-        <v>2051</v>
+        <v>909</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2610,17 +2618,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1990560640</t>
+          <t>13574310</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1990560640</t>
+          <t>https://m.place.naver.com/place/13574310</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2632,29 +2640,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>잇츠미성형외과의원</t>
+          <t>클렌피부과의원 송도점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>itsme_clinic_sd@naver.com</t>
+          <t>easy_16878@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1343-1412</t>
+          <t>032-715-4100</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 타임스페이스 A동 5층</t>
+          <t>인천광역시 연수구 컨벤시아대로230번길 54 송도닥터플러스몰 A동 5층 514-516호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.itsmeps.co.kr</t>
+          <t>http://pf.kakao.com/_FWtKC</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2664,12 +2672,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2685,17 +2693,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1425</v>
+        <v>367</v>
       </c>
       <c r="Q24" t="n">
-        <v>2255</v>
+        <v>117</v>
       </c>
       <c r="R24" t="n">
-        <v>3680</v>
+        <v>484</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2704,17 +2712,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1123500328</t>
+          <t>1983873176</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1123500328</t>
+          <t>https://m.place.naver.com/place/1983873176</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2726,34 +2734,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>오블리브의원 송도</t>
+          <t>유픽의원 송도</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>oblivclinic@naver.com</t>
+          <t>rkdgkwns43210@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1350-9120</t>
+          <t>032-256-6010</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로132번길 34 2층, 3층</t>
+          <t>인천광역시 연수구 해돋이로151번길 4 인피니티타워 6층 601, 602호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.obliv.kr/</t>
+          <t>https://www.instagram.com/upic_clinic_Songdo/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2763,7 +2771,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2783,13 +2791,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1401</v>
+        <v>512</v>
       </c>
       <c r="Q25" t="n">
-        <v>2593</v>
+        <v>5046</v>
       </c>
       <c r="R25" t="n">
-        <v>3994</v>
+        <v>5558</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2798,17 +2806,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1120924408</t>
+          <t>1794584448</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1120924408</t>
+          <t>https://m.place.naver.com/place/1794584448</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2820,29 +2828,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>오운의원 송도점</t>
+          <t>송도오라클피부과의원</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>shinebeam_songdo@naver.com</t>
+          <t>songdo_dermatology@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1644-7427</t>
+          <t>032-833-2111</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로197번길 16 리치센트럴 3층 323, 324, 325호</t>
+          <t>인천광역시 연수구 하모니로178번길 6 7층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://songdo.own-clinic.com</t>
+          <t>http://songdo-oracle.com/</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2857,7 +2865,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2877,13 +2885,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>572</v>
+        <v>824</v>
       </c>
       <c r="Q26" t="n">
-        <v>45</v>
+        <v>1870</v>
       </c>
       <c r="R26" t="n">
-        <v>617</v>
+        <v>2694</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2892,17 +2900,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1284197370</t>
+          <t>1994869691</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284197370</t>
+          <t>https://m.place.naver.com/place/1994869691</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2914,39 +2922,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>닥터포유미앤모의원</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>gabewoon@naver.com</t>
-        </is>
-      </c>
+          <t>밴스의원 송도</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1367-8057</t>
+          <t>032-710-3037</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 청능대로 93 이리옴프라자 4층</t>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 11층 1101호~1105호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/drforu_miandmo/</t>
+          <t>https://songdo.vandsclinic.co.kr/?channel=4161</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2962,22 +2966,22 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
         <v>709</v>
       </c>
       <c r="Q27" t="n">
-        <v>199</v>
+        <v>3843</v>
       </c>
       <c r="R27" t="n">
-        <v>908</v>
+        <v>4552</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2986,17 +2990,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>13574310</t>
+          <t>2015039268</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13574310</t>
+          <t>https://m.place.naver.com/place/2015039268</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3008,44 +3012,44 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>제이웰 의원 송도</t>
+          <t>플랜유의원</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>intelligent2862@naver.com</t>
+          <t>xoxozzx@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1372-9700</t>
+          <t>0507-1393-9913</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로230번길 42 아라프라자 2층</t>
+          <t>인천광역시 연수구 해돋이로 160-15 송도더퍼스트시티 2층 210호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://www.jwellclinic.com</t>
+          <t>https://www.planuclinic.co.kr/</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3056,7 +3060,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3065,13 +3069,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>873</v>
+        <v>1222</v>
       </c>
       <c r="Q28" t="n">
-        <v>1359</v>
+        <v>3157</v>
       </c>
       <c r="R28" t="n">
-        <v>2232</v>
+        <v>4379</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3080,17 +3084,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1325901584</t>
+          <t>1091669936</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1325901584</t>
+          <t>https://m.place.naver.com/place/1091669936</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3102,25 +3106,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>톡스앤필의원 송도</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>김운호피부과의원</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>cultfind@naver.com</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1426-1755</t>
+          <t>032-813-9212</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층 톡스앤필 송도점</t>
+          <t>인천광역시 연수구 앵고개로 250 연수메디칼빌딩 3층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.toxnfill4.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3130,12 +3138,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3146,22 +3154,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>656</v>
+        <v>1150</v>
       </c>
       <c r="Q29" t="n">
-        <v>5710</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>6366</v>
+        <v>1154</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3170,17 +3178,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>20618221</t>
+          <t>13240921</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20618221</t>
+          <t>https://m.place.naver.com/place/13240921</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3192,34 +3200,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>미앤아이의원 송도</t>
+          <t>맑고고운시그니처의원 인천연수동춘점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>redorange3231@naver.com</t>
+          <t>pinkclean0713@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>032-862-0075</t>
+          <t>0507-1497-1523</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 69 밀레니엄상가 608호</t>
+          <t>인천광역시 연수구 먼우금로 88 5층 501, 502호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://sd-meiclinic.co.kr/</t>
+          <t>https://www.incheonsignature.com/</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3229,7 +3237,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3240,22 +3248,22 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="Q30" t="n">
         <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>216</v>
+        <v>282</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3264,17 +3272,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>20561568</t>
+          <t>1037963149</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20561568</t>
+          <t>https://m.place.naver.com/place/1037963149</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3286,44 +3294,44 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>플랜유의원</t>
+          <t>닥터에버스의원 송도</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>xoxozzx@naver.com</t>
+          <t>dreverssd03@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1393-9913</t>
+          <t>0507-1360-7570</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-15 송도더퍼스트시티 2층 210호</t>
+          <t>인천광역시 연수구 신송로 165-17 월드메르디앙 2층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.planuclinic.co.kr/</t>
+          <t>https://evers17.co.kr/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3334,7 +3342,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3343,13 +3351,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1223</v>
+        <v>604</v>
       </c>
       <c r="Q31" t="n">
-        <v>3159</v>
+        <v>770</v>
       </c>
       <c r="R31" t="n">
-        <v>4382</v>
+        <v>1374</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3358,17 +3366,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1091669936</t>
+          <t>1614509215</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1091669936</t>
+          <t>https://m.place.naver.com/place/1614509215</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3380,29 +3388,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>김운호피부과의원</t>
+          <t>메이린의원 송도</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>cultfind@naver.com</t>
+          <t>maylin_songdo@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>032-813-9212</t>
+          <t>0507-1416-8921</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 앵고개로 250 연수메디칼빌딩 3층</t>
+          <t>인천광역시 연수구 송도국제대로 123 현대프리미엄아울렛 송도점 본관 3층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/maylin_clinic_sd/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3412,7 +3420,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3428,22 +3436,22 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1148</v>
+        <v>303</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>159</v>
       </c>
       <c r="R32" t="n">
-        <v>1152</v>
+        <v>462</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3452,17 +3460,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>13240921</t>
+          <t>1250284461</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240921</t>
+          <t>https://m.place.naver.com/place/1250284461</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3474,34 +3482,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>새로핌피부과의원 인천송도</t>
+          <t>송도스타피부과의원</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jzvgcz40jz@naver.com</t>
+          <t>songdo_dermatology@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>032-833-2777</t>
+          <t>032-434-2286</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 153 2층 207호~211호</t>
+          <t>인천광역시 연수구 컨벤시아대로 69 송도 밀레니엄</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://serophim.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3511,7 +3519,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3522,22 +3530,22 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="Q33" t="n">
-        <v>1602</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>1738</v>
+        <v>181</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3546,17 +3554,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2049567933</t>
+          <t>20188390</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2049567933</t>
+          <t>https://m.place.naver.com/place/20188390</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3625,13 +3633,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1814</v>
+        <v>1817</v>
       </c>
       <c r="Q34" t="n">
-        <v>1540</v>
+        <v>1635</v>
       </c>
       <c r="R34" t="n">
-        <v>3354</v>
+        <v>3452</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3650,7 +3658,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3662,29 +3670,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>연세마이미의원</t>
+          <t>변피부과의원</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>kti1202@naver.com</t>
+          <t>orangerealtykorea@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>032-215-1100</t>
+          <t>032-818-4333</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 166</t>
+          <t>인천광역시 연수구 원인재로 286 대림아파트 상가 301호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://mymii.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3694,12 +3702,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3719,13 +3727,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>121</v>
+        <v>257</v>
       </c>
       <c r="Q35" t="n">
-        <v>508</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>629</v>
+        <v>262</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3734,17 +3742,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>35507465</t>
+          <t>13240993</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35507465</t>
+          <t>https://m.place.naver.com/place/13240993</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3756,44 +3764,44 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>예쁨의정석의원</t>
+          <t>잇츠미성형외과의원</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jungsukbeauty@naver.com</t>
+          <t>itsme_clinic_sd@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1371-5609</t>
+          <t>0507-1343-1412</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 20 상가동 2층 216, 217, 218, 221호</t>
+          <t>인천광역시 연수구 하모니로 158 타임스페이스 A동 5층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>http://beautyjungsuk.co.kr</t>
+          <t>https://www.itsmeps.co.kr</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3809,17 +3817,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>94</v>
+        <v>1426</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>2273</v>
       </c>
       <c r="R36" t="n">
-        <v>99</v>
+        <v>3699</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3828,17 +3836,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1141240944</t>
+          <t>1123500328</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141240944</t>
+          <t>https://m.place.naver.com/place/1123500328</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3850,29 +3858,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>밴스의원 송도</t>
+          <t>실버라이닝의원</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mimimomokk@naver.com</t>
+          <t>silver_lining_songdo@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>032-710-3037</t>
+          <t>0507-1465-8112</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 11층 1101호~1105호</t>
+          <t>인천광역시 연수구 해돋이로 160-15 제2층 제201호~제205호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://songdo.vandsclinic.co.kr/?channel=4161</t>
+          <t>https://silverlining.clinic</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3903,17 +3911,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>709</v>
+        <v>200</v>
       </c>
       <c r="Q37" t="n">
-        <v>3774</v>
+        <v>237</v>
       </c>
       <c r="R37" t="n">
-        <v>4483</v>
+        <v>437</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3922,17 +3930,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2015039268</t>
+          <t>1081885317</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015039268</t>
+          <t>https://m.place.naver.com/place/1081885317</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3944,29 +3952,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>신피부과의원</t>
+          <t>리겐의원 송도</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>newskin7582@naver.com</t>
+          <t>songdo_st@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1405-7583</t>
+          <t>0507-1470-1351</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 121 센타프라자 7층 704호</t>
+          <t>인천광역시 연수구 해돋이로152번길 9 8층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/newskin7582</t>
+          <t>http://www.regainclinic.co.kr</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3981,7 +3989,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3997,17 +4005,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>380</v>
+        <v>419</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="R38" t="n">
-        <v>380</v>
+        <v>555</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4016,17 +4024,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>19873520</t>
+          <t>1724640605</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19873520</t>
+          <t>https://m.place.naver.com/place/1724640605</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4038,24 +4046,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>김지현피부과의원</t>
+          <t>드림의원</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ohhappysmc@naver.com</t>
+          <t>asdream365@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>032-817-8083</t>
+          <t>032-456-4330</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 청능대로 103 4층</t>
+          <t>인천광역시 연수구 청능대로 210 3층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4095,13 +4103,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1041</v>
+        <v>267</v>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>1051</v>
+        <v>269</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4110,17 +4118,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>13240981</t>
+          <t>36476882</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240981</t>
+          <t>https://m.place.naver.com/place/36476882</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4132,29 +4140,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>나다움의원 송도</t>
+          <t>피어봄의원 송도</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>nadaumclinic@naver.com</t>
+          <t>pieobom_sd@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>032-832-1117</t>
+          <t>032-818-8275</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 A동 210-211호</t>
+          <t>인천광역시 연수구 센트럴로 160 센트럴파크 푸르지오상가 A동 2층 201~207호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://www.나다움.com</t>
+          <t>https://songdo.pieobom.com/</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4180,7 +4188,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4189,13 +4197,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>360</v>
+        <v>532</v>
       </c>
       <c r="Q40" t="n">
-        <v>22</v>
+        <v>613</v>
       </c>
       <c r="R40" t="n">
-        <v>382</v>
+        <v>1145</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4204,17 +4212,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1498510198</t>
+          <t>37056636</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1498510198</t>
+          <t>https://m.place.naver.com/place/37056636</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4226,29 +4234,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>신비라인의원 송도</t>
+          <t>휴의원</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>shinbilineclinic2@naver.com</t>
+          <t>hueclinic1@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1332-7601</t>
+          <t>0507-1445-2881</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 3층 신비라인의원</t>
+          <t>인천광역시 연수구 용담로 115</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://www.drsinbi.com/</t>
+          <t>http://www.hue-clinic.com/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4279,17 +4287,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>461</v>
+        <v>22</v>
       </c>
       <c r="Q41" t="n">
-        <v>4512</v>
+        <v>16</v>
       </c>
       <c r="R41" t="n">
-        <v>4973</v>
+        <v>38</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4298,17 +4306,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>12913114</t>
+          <t>11783214</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12913114</t>
+          <t>https://m.place.naver.com/place/11783214</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4320,44 +4328,44 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>휴의원</t>
+          <t>새로핌피부과의원 인천송도</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>hueclinic1@naver.com</t>
+          <t>jzvgcz40jz@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1445-2881</t>
+          <t>032-833-2777</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 용담로 115</t>
+          <t>인천광역시 연수구 신송로 153 2층 207호~211호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://www.hue-clinic.com/</t>
+          <t>https://serophim.com/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4368,22 +4376,22 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>1638</v>
       </c>
       <c r="R42" t="n">
-        <v>38</v>
+        <v>1777</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4392,17 +4400,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>11783214</t>
+          <t>2049567933</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11783214</t>
+          <t>https://m.place.naver.com/place/2049567933</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4414,29 +4422,33 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>알라딘의원</t>
+          <t>파크뷰의원 송도</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>drjang77@naver.com</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>rat3427@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>sdparkview83@gmail.com</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1467-7894</t>
+          <t>032-710-1404</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 A동 4층</t>
+          <t>인천광역시 연수구 하모니로 158 B동 6층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/drjang77</t>
+          <t>https://www.youtube.com/@뷰티의정석-w9e</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4462,22 +4474,22 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="Q43" t="n">
-        <v>14</v>
+        <v>543</v>
       </c>
       <c r="R43" t="n">
-        <v>172</v>
+        <v>760</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4486,17 +4498,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1368003991</t>
+          <t>1378532253</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1368003991</t>
+          <t>https://m.place.naver.com/place/1378532253</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4508,29 +4520,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>메이린의원 송도</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>maylin_songdo@naver.com</t>
-        </is>
-      </c>
+          <t>드림피부과</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0507-1416-8921</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 123 현대프리미엄아울렛 송도점 본관 3층</t>
+          <t>인천광역시 연수구 청능대로 210 스퀘어원</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maylin_clinic_sd/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4540,7 +4544,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4556,22 +4560,22 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>303</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>461</v>
+        <v>0</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4580,17 +4584,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1250284461</t>
+          <t>4170845550</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1250284461</t>
+          <t>https://m.place.naver.com/place/4170845550</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4602,44 +4606,44 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>송도스타피부과의원</t>
+          <t>리트의원 송도</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sdbenme@naver.com</t>
+          <t>ritclinic_director@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>032-434-2286</t>
+          <t>032-833-0107</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 69 송도 밀레니엄</t>
+          <t>인천광역시 연수구 테크노파크로111번길 15 401, 402호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://ritclinic.co.kr</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4650,22 +4654,22 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>2738</v>
       </c>
       <c r="R45" t="n">
-        <v>181</v>
+        <v>2940</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4674,51 +4678,51 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>20188390</t>
+          <t>1410828317</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20188390</t>
+          <t>https://m.place.naver.com/place/1410828317</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>피부과</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>베룸마케팅</t>
+          <t>연세마이미의원</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>verummarketing@naver.com</t>
+          <t>kti1202@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1480-3039</t>
+          <t>032-215-1100</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로54번길 15-3 501,502호 알603</t>
+          <t>인천광역시 연수구 신송로 166</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/verummarketing</t>
+          <t>https://mymii.co.kr/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4753,13 +4757,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="Q46" t="n">
-        <v>5</v>
+        <v>508</v>
       </c>
       <c r="R46" t="n">
-        <v>6</v>
+        <v>628</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4768,17 +4772,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1164367460</t>
+          <t>35507465</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1164367460</t>
+          <t>https://m.place.naver.com/place/35507465</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4876,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4966,46 +4970,46 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>기능성화장품</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>코어솔루션</t>
+          <t>베룸마케팅</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>coresolution77@naver.com</t>
+          <t>verummarketing@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>070-4571-7542</t>
+          <t>0507-1480-3039</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로54번길 3 5층</t>
+          <t>인천광역시 연수구 인천타워대로54번길 15-3 501,502호 알603</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://m.livna.kr/</t>
+          <t>https://blog.naver.com/verummarketing</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5026,22 +5030,22 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5050,66 +5054,66 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2081756779</t>
+          <t>1164367460</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2081756779</t>
+          <t>https://m.place.naver.com/place/1164367460</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>내과</t>
+          <t>기능성화장품</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>송도닥터스의원</t>
+          <t>코어솔루션</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>value_trend_guide@naver.com</t>
+          <t>cs_ground@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>032-812-7338</t>
+          <t>070-4571-7542</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 165 홈플러스 송도점 B1F층</t>
+          <t>인천광역시 연수구 인천타워대로54번길 3 5층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://m.livna.kr/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5120,22 +5124,22 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>534</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>543</v>
+        <v>0</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5144,17 +5148,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>37232570</t>
+          <t>2081756779</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37232570</t>
+          <t>https://m.place.naver.com/place/2081756779</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5166,34 +5170,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>송도에이스내과의원</t>
+          <t>송도탑내과의원</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ytonysin@naver.com</t>
+          <t>read6427@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>032-858-5585</t>
+          <t>032-719-8089</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 415 판매시설동 제2층 제204호, 제207호~211호</t>
+          <t>인천광역시 연수구 인천타워대로 365 판매시설 A동 305~312호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ytonysin</t>
+          <t>http://www.sdtop.co.kr/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5203,7 +5207,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5223,13 +5227,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>487</v>
+        <v>459</v>
       </c>
       <c r="Q51" t="n">
-        <v>104</v>
+        <v>397</v>
       </c>
       <c r="R51" t="n">
-        <v>591</v>
+        <v>856</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5238,17 +5242,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1311791582</t>
+          <t>1980900955</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311791582</t>
+          <t>https://m.place.naver.com/place/1980900955</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5260,39 +5264,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>송도탑내과의원</t>
+          <t>송도닥터스의원</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>read6427@naver.com</t>
+          <t>value_trend_guide@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>032-719-8089</t>
+          <t>032-812-7338</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 365 판매시설 A동 305~312호</t>
+          <t>인천광역시 연수구 송도국제대로 165 홈플러스 송도점 B1F층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://www.sdtop.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5317,13 +5321,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>451</v>
+        <v>534</v>
       </c>
       <c r="Q52" t="n">
-        <v>395</v>
+        <v>9</v>
       </c>
       <c r="R52" t="n">
-        <v>846</v>
+        <v>543</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5332,47 +5336,51 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1980900955</t>
+          <t>37232570</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1980900955</t>
+          <t>https://m.place.naver.com/place/37232570</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>병원,의원</t>
+          <t>내과</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>피앤비의원</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>송도에이스내과의원</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ytonysin@naver.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>032-832-2251</t>
+          <t>032-858-5585</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 한진로 23 로얄프라자</t>
+          <t>인천광역시 연수구 센트럴로 415 판매시설동 제2층 제204호, 제207호~211호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ytonysin</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5382,12 +5390,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5407,13 +5415,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>198</v>
+        <v>494</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="R53" t="n">
-        <v>199</v>
+        <v>600</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5422,17 +5430,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>13241044</t>
+          <t>1311791582</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13241044</t>
+          <t>https://m.place.naver.com/place/1311791582</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5444,20 +5452,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>현대성모의원</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>피앤비의원</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>pnb_communication@naver.com</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>032-816-1367</t>
+          <t>032-832-2251</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 함박뫼로 28</t>
+          <t>인천광역시 연수구 한진로 23 로얄프라자</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5497,13 +5509,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>161</v>
+        <v>199</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5512,51 +5524,51 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>13240955</t>
+          <t>13241044</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240955</t>
+          <t>https://m.place.naver.com/place/13241044</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>비뇨의학과</t>
+          <t>병원,의원</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>유쾌한비뇨의학과의원 송도점</t>
+          <t>현대성모의원</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>uroskin_sd@naver.com</t>
+          <t>eungbo14@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>032-831-8575</t>
+          <t>032-816-1367</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 153 더마란츠타워 304호,305호</t>
+          <t>인천광역시 연수구 함박뫼로 28</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://enjoyuro.com/v2/s01/sub02_5.php</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5566,7 +5578,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5591,13 +5603,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>307</v>
+        <v>160</v>
       </c>
       <c r="Q55" t="n">
-        <v>4182</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>4489</v>
+        <v>161</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5606,61 +5618,61 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1214184965</t>
+          <t>13240955</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1214184965</t>
+          <t>https://m.place.naver.com/place/13240955</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>성형외과</t>
+          <t>비뇨의학과</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>송도 리앤스타의원</t>
+          <t>유쾌한비뇨의학과의원 송도점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sdbenme@naver.com</t>
+          <t>uroskin_sd@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1484-5030</t>
+          <t>032-831-8575</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 160 송도 푸르지오 주상복합 C동 상가 2층</t>
+          <t>인천광역시 연수구 신송로 153 더마란츠타워 304호,305호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://songdo-leenstar.com/</t>
+          <t>http://enjoyuro.com/v2/s01/sub02_5.php</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5676,22 +5688,22 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>726</v>
+        <v>307</v>
       </c>
       <c r="Q56" t="n">
-        <v>68</v>
+        <v>4281</v>
       </c>
       <c r="R56" t="n">
-        <v>794</v>
+        <v>4588</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5700,17 +5712,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1114619038</t>
+          <t>1214184965</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1114619038</t>
+          <t>https://m.place.naver.com/place/1214184965</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5722,29 +5734,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JK위드미의원</t>
+          <t>앤의원 인천연수점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>withme5401@naver.com</t>
+          <t>annds@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1402-7991</t>
+          <t>0507-1436-9703</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 165 포스코타워송도 6층 jk위드미의원</t>
+          <t>인천광역시 연수구 앵고개로264번길 30-4 영남프라자 3층 앤피부과성형외과</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://jk-withme.com/</t>
+          <t>https://annincheon.com/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5779,13 +5791,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>697</v>
+        <v>1096</v>
       </c>
       <c r="Q57" t="n">
-        <v>666</v>
+        <v>135</v>
       </c>
       <c r="R57" t="n">
-        <v>1363</v>
+        <v>1231</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5794,17 +5806,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>37485848</t>
+          <t>20370288</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37485848</t>
+          <t>https://m.place.naver.com/place/20370288</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5816,34 +5828,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>골드리버의원 인천 송도</t>
+          <t>안녕성형외과의원</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>songdo_goldriver@naver.com</t>
+          <t>hellops5400@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1433-5356</t>
+          <t>032-858-5400</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로130번길 14 3층 305호</t>
+          <t>인천광역시 연수구 해돋이로 168-2 송도에스원타워 3층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/songdo_goldriver</t>
+          <t>http://www.hellops.co.kr</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5853,7 +5865,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5873,13 +5885,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>242</v>
+        <v>3310</v>
       </c>
       <c r="Q58" t="n">
-        <v>572</v>
+        <v>347</v>
       </c>
       <c r="R58" t="n">
-        <v>814</v>
+        <v>3657</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5888,17 +5900,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>37647473</t>
+          <t>1059884727</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37647473</t>
+          <t>https://m.place.naver.com/place/1059884727</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5910,29 +5922,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>앤의원 인천연수점</t>
+          <t>송도 리앤스타의원</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>annds@naver.com</t>
+          <t>sdbenme@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1436-9703</t>
+          <t>0507-1484-5030</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 앵고개로264번길 30-4 영남프라자 3층 앤피부과성형외과</t>
+          <t>인천광역시 연수구 센트럴로 160 송도 푸르지오 주상복합 C동 상가 2층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://annincheon.com/</t>
+          <t>https://songdo-leenstar.com/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5947,7 +5959,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5967,13 +5979,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1096</v>
+        <v>734</v>
       </c>
       <c r="Q59" t="n">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="R59" t="n">
-        <v>1227</v>
+        <v>803</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5982,17 +5994,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>20370288</t>
+          <t>1114619038</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20370288</t>
+          <t>https://m.place.naver.com/place/1114619038</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6004,29 +6016,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>안녕성형외과의원</t>
+          <t>JK위드미의원</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>hellops5400@naver.com</t>
+          <t>withme5401@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>032-858-5400</t>
+          <t>0507-1402-7991</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 송도에스원타워 3층</t>
+          <t>인천광역시 연수구 컨벤시아대로 165 포스코타워송도 6층 jk위드미의원</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://www.hellops.co.kr</t>
+          <t>http://jk-withme.com/</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6036,12 +6048,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6052,7 +6064,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6061,13 +6073,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3286</v>
+        <v>696</v>
       </c>
       <c r="Q60" t="n">
-        <v>346</v>
+        <v>670</v>
       </c>
       <c r="R60" t="n">
-        <v>3632</v>
+        <v>1366</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6076,61 +6088,61 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1059884727</t>
+          <t>37485848</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1059884727</t>
+          <t>https://m.place.naver.com/place/37485848</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>소아청소년과</t>
+          <t>성형외과</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>송도맘편한소아청소년과의원</t>
+          <t>골드리버의원 인천 송도</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>dransehwan@naver.com</t>
+          <t>songdo_goldriver@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1485-1365</t>
+          <t>0507-1433-5356</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 68 2층 204호~207호, 252호, 255호~257호</t>
+          <t>인천광역시 연수구 컨벤시아대로130번길 14 3층 305호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://www.momsoa.co.kr</t>
+          <t>https://blog.naver.com/songdo_goldriver</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6146,22 +6158,22 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>789</v>
+        <v>242</v>
       </c>
       <c r="Q61" t="n">
-        <v>186</v>
+        <v>572</v>
       </c>
       <c r="R61" t="n">
-        <v>975</v>
+        <v>814</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6170,17 +6182,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1214392802</t>
+          <t>37647473</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1214392802</t>
+          <t>https://m.place.naver.com/place/37647473</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6252,10 +6264,10 @@
         <v>1727</v>
       </c>
       <c r="Q62" t="n">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="R62" t="n">
-        <v>2603</v>
+        <v>2607</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6274,41 +6286,41 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>이비인후과</t>
+          <t>소아청소년과</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>삼성드림이비인후과의원 인천송도</t>
+          <t>송도맘편한소아청소년과의원</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kjssdream@naver.com</t>
+          <t>dransehwan@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1400-0365</t>
+          <t>0507-1485-1365</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 232 더샵센트럴파크1차 E동 2층 220호</t>
+          <t>인천광역시 연수구 랜드마크로 68 2층 204호~207호, 252호, 255호~257호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://www.ssdream.co.kr/</t>
+          <t>http://www.momsoa.co.kr</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6339,17 +6351,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>649</v>
+        <v>789</v>
       </c>
       <c r="Q63" t="n">
-        <v>876</v>
+        <v>190</v>
       </c>
       <c r="R63" t="n">
-        <v>1525</v>
+        <v>979</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6358,61 +6370,61 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1576664853</t>
+          <t>1214392802</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1576664853</t>
+          <t>https://m.place.naver.com/place/1214392802</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>이비인후과</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>엘에스디자인그룹</t>
+          <t>삼성드림이비인후과의원 인천송도</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>lsdesign3993@naver.com</t>
+          <t>kjssdream@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1435-3928</t>
+          <t>0507-1400-0365</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도미래로 30 송도 BRC 스마트밸리 E동</t>
+          <t>인천광역시 연수구 센트럴로 232 더샵센트럴파크1차 E동 2층 220호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lsdesign3993</t>
+          <t>http://www.ssdream.co.kr/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6428,22 +6440,22 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>652</v>
       </c>
       <c r="Q64" t="n">
-        <v>1</v>
+        <v>889</v>
       </c>
       <c r="R64" t="n">
-        <v>1</v>
+        <v>1541</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6452,57 +6464,61 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>21905049</t>
+          <t>1576664853</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21905049</t>
+          <t>https://m.place.naver.com/place/1576664853</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>정형외과</t>
+          <t>인테리어디자인</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>벗정형외과의원 송도</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>엘에스디자인그룹</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>lsdesign3993@naver.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1379-7917</t>
+          <t>0507-1435-3928</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 6 송도중앙타워 8층</t>
+          <t>인천광역시 연수구 송도미래로 30 송도 BRC 스마트밸리 E동</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://friendos.co.kr/</t>
+          <t>https://blog.naver.com/lsdesign3993</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6527,13 +6543,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>813</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>1253</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>2066</v>
+        <v>1</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6542,17 +6558,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1925923703</t>
+          <t>21905049</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1925923703</t>
+          <t>https://m.place.naver.com/place/21905049</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6564,39 +6580,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>청담해리슨송도병원</t>
+          <t>송도 탑 정형외과의원</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>harrison_songdo@naver.com</t>
+          <t>songdo-top@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>032-832-5488</t>
+          <t>0507-1440-6767</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 157-9 3~8층</t>
+          <t>인천광역시 연수구 송도국제대로 261 GS슈퍼마켓 2층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>http://harrisonsongdo.com/main.php</t>
+          <t>https://blog.naver.com/songdo-top</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6617,17 +6633,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>661</v>
+        <v>1019</v>
       </c>
       <c r="Q66" t="n">
-        <v>1243</v>
+        <v>2962</v>
       </c>
       <c r="R66" t="n">
-        <v>1904</v>
+        <v>3981</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6636,17 +6652,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1077150743</t>
+          <t>1927029254</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1077150743</t>
+          <t>https://m.place.naver.com/place/1927029254</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6715,13 +6731,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>4508</v>
+        <v>4532</v>
       </c>
       <c r="Q67" t="n">
-        <v>2091</v>
+        <v>2112</v>
       </c>
       <c r="R67" t="n">
-        <v>6599</v>
+        <v>6644</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6740,7 +6756,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6752,39 +6768,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>송도 탑 정형외과의원</t>
+          <t>벗정형외과의원 송도</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>songdo-top@naver.com</t>
+          <t>srangb@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1440-6767</t>
+          <t>0507-1379-7917</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 261 GS슈퍼마켓 2층</t>
+          <t>인천광역시 연수구 하모니로178번길 6 송도중앙타워 8층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/songdo-top</t>
+          <t>https://friendos.co.kr/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6809,13 +6825,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1019</v>
+        <v>810</v>
       </c>
       <c r="Q68" t="n">
-        <v>2960</v>
+        <v>1299</v>
       </c>
       <c r="R68" t="n">
-        <v>3979</v>
+        <v>2109</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6824,61 +6840,61 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1927029254</t>
+          <t>1925923703</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1927029254</t>
+          <t>https://m.place.naver.com/place/1925923703</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>한방병원</t>
+          <t>정형외과</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>송도한방병원</t>
+          <t>청담해리슨송도병원</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>funkyeom@naver.com</t>
+          <t>harrison_songdo@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1661-4248</t>
+          <t>032-832-5488</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 A동 6층</t>
+          <t>인천광역시 연수구 신송로 157-9 3~8층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://송도한방병원.com</t>
+          <t>http://harrisonsongdo.com/main.php</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6903,13 +6919,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>174</v>
+        <v>664</v>
       </c>
       <c r="Q69" t="n">
-        <v>772</v>
+        <v>1243</v>
       </c>
       <c r="R69" t="n">
-        <v>946</v>
+        <v>1907</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6918,17 +6934,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1895447872</t>
+          <t>1077150743</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895447872</t>
+          <t>https://m.place.naver.com/place/1077150743</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7000,10 +7016,10 @@
         <v>974</v>
       </c>
       <c r="Q70" t="n">
-        <v>1633</v>
+        <v>1660</v>
       </c>
       <c r="R70" t="n">
-        <v>2607</v>
+        <v>2634</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7022,41 +7038,41 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>한의원</t>
+          <t>한방병원</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>인천송도 리아한의원</t>
+          <t>송도한방병원</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>songdo_lia@naver.com</t>
+          <t>funkyeom@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1331-4975</t>
+          <t>1661-4248</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 107 송도 더샵퍼스트월드상가 H동 2층 58, 59, 60호</t>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 A동 6층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/songdo_lia</t>
+          <t>http://송도한방병원.com</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7091,13 +7107,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>514</v>
+        <v>174</v>
       </c>
       <c r="Q71" t="n">
-        <v>2761</v>
+        <v>822</v>
       </c>
       <c r="R71" t="n">
-        <v>3275</v>
+        <v>996</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7106,17 +7122,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>36628584</t>
+          <t>1895447872</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36628584</t>
+          <t>https://m.place.naver.com/place/1895447872</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7128,29 +7144,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>울림한의원</t>
+          <t>자윤한의원 인천송도점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>woolimkmd@naver.com</t>
+          <t>nuk37@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1308-3652</t>
+          <t>032-721-8200</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 에스원타워 307호</t>
+          <t>인천광역시 연수구 신송로 153 더마란츠 6층 자윤한의원 인천송도점</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woolimkmd</t>
+          <t>http://i-jayoon.co.kr/sd</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7176,7 +7192,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7185,13 +7201,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>289</v>
+        <v>172</v>
       </c>
       <c r="Q72" t="n">
-        <v>2587</v>
+        <v>6114</v>
       </c>
       <c r="R72" t="n">
-        <v>2876</v>
+        <v>6286</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7200,17 +7216,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1002218506</t>
+          <t>1449901613</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1002218506</t>
+          <t>https://m.place.naver.com/place/1449901613</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7222,29 +7238,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>소통부부한의원 송도</t>
+          <t>나은내일한의원 인천 송도</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>qwlukw26@naver.com</t>
+          <t>lunarmix@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1422-3425</t>
+          <t>0507-1445-9252</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 164 5층 501호</t>
+          <t>인천광역시 연수구 신송로 153 더 마란츠타워 8층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://www.sotongbooboo-songdo.co.kr</t>
+          <t>https://www.naunmed.com/?utm_source=naver&amp;amp;utm_medium=place</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7279,13 +7295,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1079</v>
+        <v>593</v>
       </c>
       <c r="Q73" t="n">
-        <v>2287</v>
+        <v>3694</v>
       </c>
       <c r="R73" t="n">
-        <v>3366</v>
+        <v>4287</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7294,17 +7310,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1437757765</t>
+          <t>1695745929</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1437757765</t>
+          <t>https://m.place.naver.com/place/1695745929</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7316,29 +7332,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>자윤한의원 인천송도점</t>
+          <t>인천송도 리아한의원</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>nuk37@naver.com</t>
+          <t>songdo_lia@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>032-721-8200</t>
+          <t>0507-1331-4975</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 153 더마란츠 6층 자윤한의원 인천송도점</t>
+          <t>인천광역시 연수구 해돋이로 107 송도 더샵퍼스트월드상가 H동 2층 58, 59, 60호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://i-jayoon.co.kr/sd</t>
+          <t>https://blog.naver.com/songdo_lia</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7364,7 +7380,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7373,13 +7389,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>171</v>
+        <v>514</v>
       </c>
       <c r="Q74" t="n">
-        <v>6116</v>
+        <v>2812</v>
       </c>
       <c r="R74" t="n">
-        <v>6287</v>
+        <v>3326</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7388,17 +7404,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1449901613</t>
+          <t>36628584</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1449901613</t>
+          <t>https://m.place.naver.com/place/36628584</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7467,13 +7483,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="Q75" t="n">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="R75" t="n">
-        <v>4769</v>
+        <v>4771</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7492,7 +7508,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7504,34 +7520,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>나은내일한의원 인천 송도</t>
+          <t>소통부부한의원 송도</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>lunarmix@naver.com</t>
+          <t>qwlukw26@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1445-9252</t>
+          <t>0507-1422-3425</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 153 더 마란츠타워 8층</t>
+          <t>인천광역시 연수구 신송로 164 5층 501호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.naunmed.com/?utm_source=naver&amp;amp;utm_medium=place</t>
+          <t>http://www.sotongbooboo-songdo.co.kr</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7541,7 +7557,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7552,7 +7568,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7561,13 +7577,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>590</v>
+        <v>1084</v>
       </c>
       <c r="Q76" t="n">
-        <v>3645</v>
+        <v>2294</v>
       </c>
       <c r="R76" t="n">
-        <v>4235</v>
+        <v>3378</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7576,17 +7592,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1695745929</t>
+          <t>1437757765</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695745929</t>
+          <t>https://m.place.naver.com/place/1437757765</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
